--- a/reports/devops-jobs-israel-2026-W24.xlsx
+++ b/reports/devops-jobs-israel-2026-W24.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-08T11:16:09</t>
+    <t xml:space="preserve">2026-06-09T09:59:56</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -351,6 +351,15 @@
     <t xml:space="preserve">2026-05-28</t>
   </si>
   <si>
+    <t xml:space="preserve">Software Architect - DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+  </si>
+  <si>
     <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
   </si>
   <si>
@@ -402,21 +411,6 @@
     <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Software Engineer – CX Platform Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, ELK/Elastic, MySQL, Redis, Kafka, Security, Observability, Snowflake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8553634002</t>
-  </si>
-  <si>
     <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
@@ -432,7 +426,7 @@
     <t xml:space="preserve">DevOps Engineer (Remote)</t>
   </si>
   <si>
-    <t xml:space="preserve">Washington, United States</t>
+    <t xml:space="preserve">Boston, Massachusetts, United States</t>
   </si>
   <si>
     <t xml:space="preserve">Israel (other)</t>
@@ -441,54 +435,54 @@
     <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Security, Argo CD, Observability</t>
   </si>
   <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010969004</t>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010968004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
     <t xml:space="preserve">DevSecOps</t>
   </si>
   <si>
@@ -558,40 +552,361 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4422246034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4425198243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-insait-4422376363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-devops-engineer-at-abra-4425003795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Administrator &amp; DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appdome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-administrator-devops-at-appdome-4421928922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zafran Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4423379202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-entrio-4419290857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4425242600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4425654229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-4421988364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hof HaCarmel Regional Council, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4422250329</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4414190903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (36354)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36354-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4425486507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-commit-4425110784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfraEdge IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infraedge-il-4421944139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4422931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4421593110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-dream-4335498627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeva Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4421926577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-millennium-4425034300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-engineer-at-intel-4424414559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sola Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sola-security-4425029092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagomi Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-nagomi-security-4425014911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-rhino-federated-computing-4405650446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GK8 by Galaxy (Nasdaq: GLXY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gk8-by-galaxy-nasdaq-glxy-4423387010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415535201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mastercard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-mastercard-4421916027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SVP, Site Reliability Engineering (AI Innovation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeepRec.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/svp-site-reliability-engineering-ai-innovation-at-deeprec-ai-4422357271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22765 - Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22765-reliability-engineer-sre-at-qualitest-4420738290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lenovo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-lenovo-4424600261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-comblack-4421694778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4424338342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-entrio-4419290857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autodesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-autodesk-4403368852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4419674925</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4403682415</t>
   </si>
   <si>
     <t xml:space="preserve">SailPoint</t>
@@ -600,618 +915,309 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
   </si>
   <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Backend Engineer (GCP Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azimut.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-backend-engineer-gcp-infrastructure-at-azimut-ai-4422252173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vi</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vi-4421931598</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops</t>
+    <t xml:space="preserve">Razel Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-razel-group-4422251838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer-2617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shabak - Israeli Security Agency - Career</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-2617-at-shabak-israeli-security-agency-career-4419681440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roboteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-roboteam-4419684684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4425543714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Time Group - Software Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-real-time-group-software-solutions-4421942748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-ai-4422235857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4425237881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4425076264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Infrastructure Engineer（SRE）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">株式会社GA technologies / GA technologies Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-infrastructure-engineer%EF%BC%88sre%EF%BC%89-at-%E6%A0%AA%E5%BC%8F%E4%BC%9A%E7%A4%BEga-technologies-ga-technologies-co-ltd-4425654538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4421930625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHY System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Elbit Systems Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codsec-4422337649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4425439235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Administrator &amp; DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appdome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-administrator-devops-at-appdome-4421928922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-engineer-at-intel-4424414559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludeo</t>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-elbit-systems-israel-4421911706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peax dorcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-at-peax-dorcom-4421925931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🚀 Senior AI Systems &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CyberLabs Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%F0%9F%9A%80-senior-ai-systems-infrastructure-engineer-at-cyberlabs-israel-4421935643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4425603835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-lead-at-akamai-technologies-4422930991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-platform-engineer-at-gotfriends-4421571443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetNut.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4420191774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering Manager (SRE Team) - Hands-On</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipalti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-manager-sre-team-hands-on-at-tipalti-4412578041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
   </si>
   <si>
     <t xml:space="preserve">Security</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sola Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sola-security-4425029092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paz - yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yaqum, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-paz-yellow-4425456877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ur-tech-jobs-4425078418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagomi Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-nagomi-security-4425014911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-commit-4425110784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer-2617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shabak - Israeli Security Agency - Career</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-2617-at-shabak-israeli-security-agency-career-4419681440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4422931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-youcc-technologies-ltd-4421927527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4421593110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4421926577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeva Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mastercard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-mastercard-4421916027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22765 - Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22765-reliability-engineer-sre-at-qualitest-4420738290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-millennium-4425034300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-comblack-4421694778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensi.AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sensi-ai-4421835860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4403682415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-devops-engineer-at-abra-4425003795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insait</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-insait-4422376363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4425198243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zafran Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4423379202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GK8 by Galaxy (Nasdaq: GLXY)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gk8-by-galaxy-nasdaq-glxy-4423387010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-dream-4335498627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Private Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4414601125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-frontend-infrastructure-engineer-core-team-at-connecteam-4365751301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roboteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-roboteam-4419684684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artivion EMEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-artivion-emea-4423879474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-dialog-4419694286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4421583725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4425076264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Interceptor System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skapion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-interceptor-system-engineer-at-skapion-4422362464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-elbit-systems-israel-4421911706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-system-engineer-at-iai-israel-aerospace-industries-4418729987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seeker System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/seeker-system-engineer-at-skapion-4422362465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Microsoft Systems Infrastructure Engineer (1006270)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-systems-infrastructure-engineer-1006270-at-elad-software-systems-4422877678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frontend Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BTC searching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/frontend-infrastructure-engineer-at-btc-searching-4422498571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🚀 Senior AI Systems &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CyberLabs Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%F0%9F%9A%80-senior-ai-systems-infrastructure-engineer-at-cyberlabs-israel-4421935643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SVP, Site Reliability Engineering (AI Innovation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeepRec.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/svp-site-reliability-engineering-ai-innovation-at-deeprec-ai-4422357271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-lead-at-priority-software-4424019406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4419681559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-4412739664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-platform-engineer-at-gotfriends-4421571443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
+    <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
+    <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -1251,10 +1257,10 @@
     <t xml:space="preserve">Percent</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3%</t>
+    <t xml:space="preserve">58.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1278,48 +1284,21 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4398384580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1329,6 +1308,21 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation student- Jerusalem</t>
   </si>
   <si>
@@ -1356,6 +1350,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-cato-networks-4398801612</t>
+  </si>
+  <si>
     <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
   </si>
   <si>
@@ -1371,42 +1377,27 @@
     <t xml:space="preserve">iFOR FINTECH</t>
   </si>
   <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Support Specialist - Temporary position</t>
   </si>
   <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1431,7 +1422,10 @@
     <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-support-engineer-level-1132895</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-codevalue-4421843930</t>
   </si>
   <si>
     <t xml:space="preserve">Menora Mivtachim Group</t>
@@ -1443,16 +1437,31 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-31</t>
@@ -1479,27 +1488,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (24892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4410129423</t>
-  </si>
-  <si>
     <t xml:space="preserve">qb Systems ltd.</t>
   </si>
   <si>
@@ -1509,15 +1497,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1527,19 +1506,19 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
+    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Git</t>
@@ -1694,7 +1673,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7">
@@ -1710,7 +1689,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -1718,7 +1697,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>510</v>
+        <v>532</v>
       </c>
     </row>
     <row r="10">
@@ -1790,7 +1769,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
@@ -1817,46 +1796,38 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B3" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="B6" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1873,95 +1844,95 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="B2" s="3">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B9" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>505</v>
+        <v>398</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>394</v>
+        <v>498</v>
       </c>
       <c r="B11" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>506</v>
+        <v>396</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -1969,7 +1940,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>393</v>
+        <v>499</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
@@ -1977,7 +1948,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>507</v>
+        <v>395</v>
       </c>
       <c r="B14" s="3">
         <v>5</v>
@@ -1985,15 +1956,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>392</v>
+        <v>500</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -2021,13 +1992,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2">
@@ -2038,10 +2009,10 @@
         <v>42</v>
       </c>
       <c r="C2" s="3">
-        <v>13.5</v>
+        <v>19.9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2050,88 +2021,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C3" s="3">
-        <v>32.8</v>
+        <v>34.2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.6</v>
+        <v>8.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.6</v>
+        <v>3.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.6</v>
+        <v>37.6</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>16.4</v>
+        <v>17.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.2</v>
+        <v>14.6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2142,9 +2113,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="2" max="2" width="49" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2215,7 +2186,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -2247,7 +2218,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -2279,7 +2250,7 @@
         <v>48</v>
       </c>
       <c r="J4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2311,7 +2282,7 @@
         <v>48</v>
       </c>
       <c r="J5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2343,7 +2314,7 @@
         <v>48</v>
       </c>
       <c r="J6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2375,7 +2346,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -2407,7 +2378,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -2439,7 +2410,7 @@
         <v>65</v>
       </c>
       <c r="J9" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -2471,7 +2442,7 @@
         <v>71</v>
       </c>
       <c r="J10" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -2503,7 +2474,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -2535,7 +2506,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -2567,7 +2538,7 @@
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -2599,7 +2570,7 @@
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2631,7 +2602,7 @@
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2663,7 +2634,7 @@
         <v>91</v>
       </c>
       <c r="J16" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -2695,7 +2666,7 @@
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
@@ -2727,7 +2698,7 @@
         <v>41</v>
       </c>
       <c r="J18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -2759,7 +2730,7 @@
         <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -2791,7 +2762,7 @@
         <v>105</v>
       </c>
       <c r="J20" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -2823,7 +2794,7 @@
         <v>109</v>
       </c>
       <c r="J21" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -2831,10 +2802,10 @@
         <v>110</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>59</v>
@@ -2843,155 +2814,155 @@
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="J22" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J23" s="3">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="J24" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="J25" s="3">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>59</v>
@@ -3003,91 +2974,91 @@
         <v>68</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="J28" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>58</v>
@@ -3099,30 +3070,30 @@
         <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>59</v>
@@ -3131,30 +3102,30 @@
         <v>38</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="J31" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>59</v>
@@ -3163,30 +3134,30 @@
         <v>68</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>59</v>
@@ -3195,30 +3166,30 @@
         <v>68</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>59</v>
@@ -3227,33 +3198,33 @@
         <v>38</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>68</v>
@@ -3263,27 +3234,27 @@
         <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J35" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>38</v>
@@ -3293,21 +3264,21 @@
         <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J36" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>59</v>
@@ -3319,27 +3290,27 @@
         <v>38</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>109</v>
       </c>
       <c r="J37" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>59</v>
@@ -3355,27 +3326,27 @@
         <v>24</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J38" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>68</v>
@@ -3385,24 +3356,24 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J39" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>183</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>59</v>
@@ -3415,24 +3386,24 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="J40" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>59</v>
@@ -3445,18 +3416,18 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="J41" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>132</v>
+        <v>187</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>188</v>
@@ -3465,7 +3436,7 @@
         <v>189</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>68</v>
@@ -3478,21 +3449,21 @@
         <v>190</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="J42" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>59</v>
@@ -3505,24 +3476,24 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J43" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>59</v>
@@ -3535,27 +3506,27 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>48</v>
+        <v>196</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>195</v>
+        <v>130</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>68</v>
@@ -3568,15 +3539,15 @@
         <v>198</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>199</v>
@@ -3598,27 +3569,27 @@
         <v>201</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="J46" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="D47" s="3" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
@@ -3628,10 +3599,10 @@
         <v>203</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="J47" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3642,23 +3613,23 @@
         <v>205</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>207</v>
+        <v>59</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="J48" s="3">
         <v>0</v>
@@ -3666,13 +3637,13 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>59</v>
@@ -3685,24 +3656,24 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>119</v>
+        <v>180</v>
       </c>
       <c r="J49" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>211</v>
+        <v>130</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>59</v>
@@ -3715,10 +3686,10 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="J50" s="3">
         <v>0</v>
@@ -3726,16 +3697,16 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>214</v>
+        <v>130</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>217</v>
+        <v>59</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>68</v>
@@ -3745,72 +3716,70 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>219</v>
+        <v>44</v>
       </c>
       <c r="J51" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>59</v>
+        <v>215</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>221</v>
-      </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="J52" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="J53" s="3">
         <v>0</v>
@@ -3818,29 +3787,29 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="J54" s="3">
         <v>0</v>
@@ -3848,16 +3817,16 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>59</v>
+        <v>225</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>68</v>
@@ -3867,40 +3836,40 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>232</v>
+        <v>153</v>
       </c>
       <c r="J55" s="3">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>207</v>
+        <v>136</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="J56" s="3">
         <v>0</v>
@@ -3908,13 +3877,13 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>59</v>
@@ -3927,27 +3896,27 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>238</v>
+        <v>130</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>207</v>
+        <v>59</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>68</v>
@@ -3957,24 +3926,24 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>59</v>
@@ -3987,114 +3956,114 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>243</v>
+        <v>153</v>
       </c>
       <c r="J59" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>244</v>
+        <v>72</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>219</v>
+        <v>44</v>
       </c>
       <c r="J60" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>248</v>
+        <v>200</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J61" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>189</v>
+        <v>244</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>59</v>
@@ -4107,10 +4076,10 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="J63" s="3">
         <v>1</v>
@@ -4118,16 +4087,16 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>132</v>
+        <v>248</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>256</v>
+        <v>185</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>68</v>
@@ -4137,84 +4106,84 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J64" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>167</v>
+        <v>215</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="J65" s="3">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>48</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>265</v>
+        <v>185</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>59</v>
@@ -4227,54 +4196,54 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J67" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>267</v>
+        <v>72</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J68" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>270</v>
+        <v>72</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>59</v>
@@ -4287,24 +4256,24 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>48</v>
+        <v>196</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>59</v>
@@ -4317,27 +4286,27 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>44</v>
+        <v>266</v>
       </c>
       <c r="J70" s="3">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>276</v>
+        <v>130</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>206</v>
+        <v>268</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>207</v>
+        <v>136</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>68</v>
@@ -4347,144 +4316,144 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="J71" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J72" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>72</v>
+        <v>273</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>186</v>
+        <v>275</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="J73" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>286</v>
+        <v>224</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>138</v>
+        <v>225</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>235</v>
+        <v>280</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="J75" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>59</v>
@@ -4497,87 +4466,87 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>235</v>
+        <v>286</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>189</v>
+        <v>268</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>48</v>
+        <v>196</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>75</v>
+        <v>248</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="J78" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>297</v>
+        <v>248</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>179</v>
+        <v>291</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>68</v>
@@ -4587,56 +4556,54 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J79" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>300</v>
+        <v>217</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>186</v>
+        <v>294</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>221</v>
-      </c>
+      <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J80" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>59</v>
@@ -4649,27 +4616,27 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J81" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>68</v>
@@ -4679,24 +4646,24 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>132</v>
+        <v>301</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>59</v>
@@ -4704,32 +4671,34 @@
       <c r="E83" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F83" s="3"/>
+      <c r="F83" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="J83" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>132</v>
+        <v>305</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>68</v>
@@ -4739,51 +4708,51 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>132</v>
+        <v>309</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>219</v>
+        <v>153</v>
       </c>
       <c r="J85" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>200</v>
@@ -4792,31 +4761,31 @@
         <v>59</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>219</v>
+        <v>48</v>
       </c>
       <c r="J86" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>59</v>
@@ -4829,40 +4798,40 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J87" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>317</v>
+        <v>130</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>207</v>
+        <v>59</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>243</v>
+        <v>122</v>
       </c>
       <c r="J88" s="3">
         <v>22</v>
@@ -4870,46 +4839,46 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>320</v>
+        <v>130</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>186</v>
+        <v>307</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J89" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>68</v>
@@ -4919,27 +4888,27 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>243</v>
+        <v>196</v>
       </c>
       <c r="J90" s="3">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>327</v>
+        <v>275</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>68</v>
@@ -4949,24 +4918,24 @@
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>71</v>
       </c>
       <c r="J91" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>330</v>
+        <v>217</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>310</v>
+        <v>200</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>59</v>
@@ -4979,27 +4948,27 @@
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="J92" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>188</v>
+        <v>328</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>68</v>
@@ -5009,13 +4978,13 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="J93" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -5023,13 +4992,13 @@
         <v>325</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>334</v>
+        <v>177</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>335</v>
+        <v>185</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>68</v>
@@ -5039,21 +5008,21 @@
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="J94" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>200</v>
@@ -5069,10 +5038,10 @@
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="J95" s="3">
         <v>0</v>
@@ -5080,73 +5049,73 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>342</v>
+        <v>68</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>48</v>
+        <v>266</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>200</v>
+        <v>340</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>38</v>
+        <v>341</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="J97" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>59</v>
@@ -5159,24 +5128,24 @@
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J98" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>196</v>
+        <v>347</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>351</v>
+        <v>185</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>59</v>
@@ -5189,10 +5158,10 @@
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="J99" s="3">
         <v>0</v>
@@ -5200,16 +5169,16 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>355</v>
+        <v>185</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>68</v>
@@ -5219,27 +5188,27 @@
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J100" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>68</v>
@@ -5249,27 +5218,27 @@
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="J101" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>68</v>
@@ -5279,24 +5248,24 @@
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J102" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>183</v>
+        <v>360</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>59</v>
@@ -5309,54 +5278,54 @@
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="J103" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J104" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>59</v>
@@ -5369,27 +5338,27 @@
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>48</v>
       </c>
       <c r="J105" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>372</v>
+        <v>130</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>327</v>
+        <v>189</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>68</v>
@@ -5399,27 +5368,27 @@
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="J106" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>38</v>
@@ -5429,27 +5398,27 @@
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="J107" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>186</v>
+        <v>275</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>38</v>
@@ -5459,87 +5428,87 @@
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>232</v>
+        <v>169</v>
       </c>
       <c r="J108" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>71</v>
+        <v>196</v>
       </c>
       <c r="J109" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>382</v>
+        <v>236</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>327</v>
+        <v>200</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="J110" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>56</v>
+        <v>381</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>186</v>
+        <v>275</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>38</v>
@@ -5549,27 +5518,27 @@
         <v>23</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>119</v>
+        <v>266</v>
       </c>
       <c r="J111" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>253</v>
+        <v>385</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>183</v>
+        <v>386</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>59</v>
+        <v>387</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>68</v>
@@ -5579,17 +5548,47 @@
         <v>23</v>
       </c>
       <c r="H112" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="J112" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="I112" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="J112" s="3">
-        <v>1</v>
+      <c r="B113" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J113" s="3">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J112"/>
+  <autoFilter ref="A1:J113"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5702,6 +5701,7 @@
     <hyperlink ref="H110" r:id="rId109"/>
     <hyperlink ref="H111" r:id="rId110"/>
     <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5709,9 +5709,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="2" width="49" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5743,70 +5743,70 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>36</v>
+        <v>178</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>47</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>188</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>36</v>
+        <v>202</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>50</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>51</v>
+        <v>204</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>185</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>52</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5814,18 +5814,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>195</v>
+        <v>130</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5833,18 +5833,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5852,18 +5852,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>211</v>
+        <v>130</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5871,18 +5871,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5890,18 +5890,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>225</v>
+        <v>130</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5914,13 +5914,13 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>206</v>
+        <v>268</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5928,18 +5928,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>236</v>
+        <v>289</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5947,18 +5947,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>237</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>250</v>
+        <v>301</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>251</v>
+        <v>302</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5966,15 +5966,15 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>252</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>261</v>
+        <v>314</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>200</v>
@@ -5985,15 +5985,15 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>262</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>270</v>
+        <v>325</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>271</v>
+        <v>217</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>200</v>
@@ -6004,18 +6004,18 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>272</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>235</v>
+        <v>327</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>288</v>
+        <v>328</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>186</v>
+        <v>329</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6023,18 +6023,18 @@
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>289</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>290</v>
+        <v>325</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>291</v>
+        <v>177</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -6042,18 +6042,18 @@
         <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>292</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>235</v>
+        <v>332</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>293</v>
+        <v>333</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -6061,18 +6061,18 @@
         <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>294</v>
+        <v>334</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>132</v>
+        <v>346</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>309</v>
+        <v>347</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>310</v>
+        <v>185</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -6080,18 +6080,18 @@
         <v>23</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>311</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -6099,18 +6099,18 @@
         <v>23</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>341</v>
+        <v>189</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -6118,18 +6118,18 @@
         <v>23</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>196</v>
+        <v>363</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>351</v>
+        <v>200</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -6137,18 +6137,18 @@
         <v>23</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>369</v>
+        <v>130</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -6156,7 +6156,7 @@
         <v>23</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -6197,31 +6197,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>221</v>
+        <v>394</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B4" s="3">
         <v>22</v>
@@ -6229,15 +6229,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B6" s="3">
         <v>19</v>
@@ -6245,15 +6245,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>396</v>
+        <v>303</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B8" s="3">
         <v>15</v>
@@ -6261,15 +6261,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B10" s="3">
         <v>13</v>
@@ -6277,7 +6277,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -6285,15 +6285,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
@@ -6301,7 +6301,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -6309,7 +6309,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -6317,7 +6317,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -6330,7 +6330,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6339,7 +6339,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2">
@@ -6360,7 +6360,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6376,31 +6376,31 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>116</v>
+        <v>217</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6416,7 +6416,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6424,7 +6424,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6432,7 +6432,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6440,7 +6440,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6448,7 +6448,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6456,10 +6456,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>302</v>
+        <v>114</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6470,23 +6470,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="2">
@@ -6522,7 +6522,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C4" s="3">
         <v>14.0</v>
@@ -6536,10 +6536,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="C5" s="3">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -6550,13 +6550,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3">
-        <v>7.2</v>
+        <v>10.9</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -6578,7 +6578,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C8" s="3">
         <v>6.2</v>
@@ -6592,7 +6592,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C9" s="3">
         <v>5.8</v>
@@ -6606,13 +6606,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="C10" s="3">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -6620,13 +6620,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="C11" s="3">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -6634,7 +6634,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -6648,13 +6648,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>302</v>
+        <v>145</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6662,13 +6662,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>345</v>
+        <v>140</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6676,10 +6676,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>382</v>
+        <v>177</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6690,13 +6690,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>148</v>
+        <v>236</v>
       </c>
       <c r="C16" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6716,15 +6716,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -6738,10 +6738,10 @@
         <v>68</v>
       </c>
       <c r="B3" s="3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4">
@@ -6749,10 +6749,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -6771,7 +6771,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2">
@@ -6779,15 +6779,15 @@
         <v>59</v>
       </c>
       <c r="B2" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -6795,38 +6795,46 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>167</v>
+        <v>215</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>124</v>
+        <v>225</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>217</v>
+        <v>127</v>
       </c>
       <c r="B8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6839,7 +6847,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6851,10 +6859,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6866,10 +6874,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6886,7 +6894,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>78</v>
@@ -6895,19 +6903,19 @@
         <v>79</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6918,31 +6926,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>419</v>
+        <v>343</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>420</v>
+        <v>344</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>421</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>422</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>424</v>
+        <v>345</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>65</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4">
@@ -6950,31 +6958,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="F4" s="3">
+        <v>74</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="F4" s="3">
-        <v>83</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="5">
@@ -6982,31 +6990,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>431</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>432</v>
+        <v>185</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="F5" s="3">
         <v>74</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="6">
@@ -7014,31 +7022,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F6" s="3">
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7">
@@ -7046,28 +7054,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>440</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="F7" s="3">
         <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>44</v>
@@ -7078,31 +7086,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="F8" s="3">
+        <v>54</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="F8" s="3">
-        <v>52</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>447</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -7110,31 +7118,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>449</v>
+        <v>252</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>310</v>
+        <v>253</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="F9" s="3">
         <v>52</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>71</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10">
@@ -7142,31 +7150,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="F10" s="3">
+        <v>52</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="F10" s="3">
-        <v>51</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>456</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>219</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -7174,28 +7182,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>457</v>
+        <v>429</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F11" s="3">
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>44</v>
@@ -7206,31 +7214,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F12" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>44</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13">
@@ -7238,31 +7246,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>465</v>
+        <v>444</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>466</v>
+        <v>200</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F13" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>468</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>141</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -7270,31 +7278,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>183</v>
+        <v>463</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>450</v>
+        <v>418</v>
       </c>
       <c r="F14" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>465</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>474</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15">
@@ -7302,31 +7310,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>453</v>
+        <v>351</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>475</v>
+        <v>181</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>197</v>
+        <v>294</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="F15" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>478</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16">
@@ -7334,31 +7342,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>479</v>
+        <v>351</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="F16" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>71</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17">
@@ -7366,31 +7374,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>305</v>
+        <v>473</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>189</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="F17" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>44</v>
+        <v>476</v>
       </c>
     </row>
     <row r="18">
@@ -7398,31 +7406,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>305</v>
+        <v>478</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>189</v>
+        <v>275</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>450</v>
+        <v>418</v>
       </c>
       <c r="F18" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>44</v>
+        <v>481</v>
       </c>
     </row>
     <row r="19">
@@ -7430,31 +7438,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>361</v>
+        <v>200</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F19" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -7462,31 +7470,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>453</v>
+        <v>486</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>493</v>
+        <v>188</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="F20" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -7494,31 +7502,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>496</v>
+        <v>443</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>123</v>
+        <v>489</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>124</v>
+        <v>200</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F21" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W24.xlsx
+++ b/reports/devops-jobs-israel-2026-W24.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="520">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-09T09:59:56</t>
+    <t xml:space="preserve">2026-06-10T10:18:17</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,15 +57,12 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9%</t>
+    <t xml:space="preserve">0.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0%</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maintained by</t>
   </si>
   <si>
@@ -324,6 +321,18 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7598823&amp;gh_jid=7598823</t>
   </si>
   <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Linux, Python, Prometheus, Grafana, New Relic, Networking, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7957880&amp;gh_jid=7957880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior DevOps</t>
   </si>
   <si>
@@ -501,6 +510,15 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
   </si>
   <si>
+    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Devops Engineer</t>
   </si>
   <si>
@@ -552,6 +570,18 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
   </si>
   <si>
+    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-abra-4425003795</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVIDIA AI</t>
   </si>
   <si>
@@ -573,33 +603,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4425198243</t>
   </si>
   <si>
-    <t xml:space="preserve">Insait</t>
+    <t xml:space="preserve">IT Administrator &amp; DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appdome</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-insait-4422376363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-devops-engineer-at-abra-4425003795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Administrator &amp; DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appdome</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-administrator-devops-at-appdome-4421928922</t>
   </si>
   <si>
@@ -612,70 +624,79 @@
     <t xml:space="preserve">2026-06-05</t>
   </si>
   <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrio</t>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4425654229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4425242600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Intelligence</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-entrio-4419290857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4425242600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4425654229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural Intelligence</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
   </si>
   <si>
-    <t xml:space="preserve">Stealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-4421988364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4414190903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizon Technologies LTD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-horizon-technologies-ltd-4423126060</t>
   </si>
   <si>
     <t xml:space="preserve">Hof HaCarmel Regional Council, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4422250329</t>
   </si>
   <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4414190903</t>
+    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Engineer (36354)</t>
@@ -687,6 +708,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36354-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4425486507</t>
   </si>
   <si>
+    <t xml:space="preserve">Sola Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sola-security-4425029092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VoIP/DevOps Engineer (SIP Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Squaretalk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/voip-devops-engineer-sip-focus-at-squaretalk-4426348262</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Team Leader</t>
   </si>
   <si>
@@ -708,25 +747,271 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infraedge-il-4421944139</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4422931002</t>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-engineer-at-intel-4424414559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paz - yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yaqum, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-paz-yellow-4425456877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4426710226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SailPoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vi-4421931598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4425603835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ur-tech-jobs-4425565373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-quantum-machines-4412371822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-youcc-technologies-ltd-4421927527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22765 - Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22765-reliability-engineer-sre-at-qualitest-4420738290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeva Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mastercard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-mastercard-4421916027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagomi Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-nagomi-security-4425014911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-millennium-4425034300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lenovo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-lenovo-4424600261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-comblack-4421694778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Private Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4414601125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4421926577</t>
   </si>
   <si>
     <t xml:space="preserve">Gotfriends</t>
@@ -735,532 +1020,274 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4421593110</t>
   </si>
   <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-dream-4335498627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeva Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4421926577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-millennium-4425034300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-engineer-at-intel-4424414559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sola Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sola-security-4425029092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagomi Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-nagomi-security-4425014911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-rhino-federated-computing-4405650446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GK8 by Galaxy (Nasdaq: GLXY)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gk8-by-galaxy-nasdaq-glxy-4423387010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415535201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mastercard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-mastercard-4421916027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SVP, Site Reliability Engineering (AI Innovation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeepRec.ai</t>
+    <t xml:space="preserve">Senior Cloud Infrastructure Engineer（SRE）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">株式会社GA technologies / GA technologies Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-infrastructure-engineer%EF%BC%88sre%EF%BC%89-at-%E6%A0%AA%E5%BC%8F%E4%BC%9A%E7%A4%BEga-technologies-ga-technologies-co-ltd-4425654538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roboteam</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/svp-site-reliability-engineering-ai-innovation-at-deeprec-ai-4422357271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22765 - Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22765-reliability-engineer-sre-at-qualitest-4420738290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff DevOps Engineer (Secure Cloud Access)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-secure-cloud-access-at-palo-alto-networks-4420146470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lenovo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-lenovo-4424600261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-comblack-4421694778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4403682415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SailPoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Backend Engineer (GCP Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azimut.ai</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-roboteam-4419684684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4425543714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Time Group - Software Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-real-time-group-software-solutions-4421942748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-ai-4422235857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer - 236606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-236606-at-experis-israel-4422794863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (LCM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-lcm-at-extreme-4426742604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-infrastructure-engineer-at-comblack-4425497939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4421930625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-elbit-systems-israel-4421911706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHY System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4422797374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-quanthealth-4425994726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-platform-engineer-at-gotfriends-4421571443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-lead-at-akamai-technologies-4422930991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetNut.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4420191774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
   </si>
   <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-backend-engineer-gcp-infrastructure-at-azimut-ai-4422252173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vi-4421931598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razel Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-razel-group-4422251838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer-2617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shabak - Israeli Security Agency - Career</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-2617-at-shabak-israeli-security-agency-career-4419681440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roboteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-roboteam-4419684684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4425543714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Time Group - Software Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-real-time-group-software-solutions-4421942748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-ai-4422235857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4425237881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grafana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
   </si>
   <si>
     <t xml:space="preserve">Junior</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4425076264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Infrastructure Engineer（SRE）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">株式会社GA technologies / GA technologies Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-infrastructure-engineer%EF%BC%88sre%EF%BC%89-at-%E6%A0%AA%E5%BC%8F%E4%BC%9A%E7%A4%BEga-technologies-ga-technologies-co-ltd-4425654538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4421930625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-elbit-systems-israel-4421911706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-at-peax-dorcom-4421925931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🚀 Senior AI Systems &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CyberLabs Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%F0%9F%9A%80-senior-ai-systems-infrastructure-engineer-at-cyberlabs-israel-4421935643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4425603835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-lead-at-akamai-technologies-4422930991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-platform-engineer-at-gotfriends-4421571443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NetNut.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4420191774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering Manager (SRE Team) - Hands-On</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipalti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-manager-sre-team-hands-on-at-tipalti-4412578041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1%</t>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1284,105 +1311,123 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-cato-networks-4398801612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-cato-networks-4398801612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
   </si>
   <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
   </si>
   <si>
@@ -1395,6 +1440,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
   </si>
   <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Support Specialist - Temporary position</t>
   </si>
   <si>
@@ -1404,7 +1464,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
   </si>
   <si>
     <t xml:space="preserve">Level</t>
@@ -1422,10 +1488,28 @@
     <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-support-engineer-level-1132895</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-codevalue-4421843930</t>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aristocrat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
   </si>
   <si>
     <t xml:space="preserve">Menora Mivtachim Group</t>
@@ -1437,64 +1521,10 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1509,16 +1539,16 @@
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
+    <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Git</t>
@@ -1673,7 +1703,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7">
@@ -1681,7 +1711,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1689,7 +1719,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -1697,7 +1727,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>532</v>
+        <v>542</v>
       </c>
     </row>
     <row r="10">
@@ -1705,7 +1735,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1721,7 +1751,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1730,26 +1760,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1758,26 +1788,26 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1793,39 +1823,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B2" s="3">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>421</v>
+        <v>463</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1844,23 +1874,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B3" s="3">
         <v>28</v>
@@ -1868,63 +1898,63 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>494</v>
+        <v>406</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="B5" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>399</v>
+        <v>507</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>404</v>
+        <v>508</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>498</v>
+        <v>404</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
@@ -1932,39 +1962,39 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>396</v>
+        <v>509</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>499</v>
+        <v>402</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -1986,123 +2016,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3">
-        <v>19.9</v>
+        <v>13.3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="3">
-        <v>34.2</v>
+        <v>43.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.0</v>
+        <v>8.3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.0</v>
+        <v>2.9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>37.6</v>
+        <v>29.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.5</v>
+        <v>20.1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2127,706 +2157,706 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J2" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J3" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="J4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="I6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="I7" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J7" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="I8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J8" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="J9" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="J10" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="I11" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J11" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="I12" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J12" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="I13" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J13" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="I14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J14" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I15" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J15" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="3" t="s">
+      <c r="I16" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="J16" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="I17" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J17" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="I18" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J18" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="I19" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J19" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="J20" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="J21" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J22" s="3">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -2834,319 +2864,319 @@
         <v>113</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="I23" s="3" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="J23" s="3">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J24" s="3">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="3" t="s">
+      <c r="I25" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="J25" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>45</v>
+        <v>126</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="I26" s="3" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="J26" s="3">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="D27" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="I27" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J27" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="C28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="I28" s="3" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="J28" s="3">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="E29" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="I29" s="3" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="J29" s="3">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="D30" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="I30" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J30" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="I31" s="3" t="s">
-        <v>153</v>
+        <v>40</v>
       </c>
       <c r="J31" s="3">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="3" t="s">
+      <c r="I32" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J32" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -3154,31 +3184,31 @@
         <v>157</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>158</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>159</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J33" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34">
@@ -3186,31 +3216,31 @@
         <v>160</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>161</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>162</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J34" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35">
@@ -3218,140 +3248,142 @@
         <v>163</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="J35" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>168</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>169</v>
+        <v>40</v>
       </c>
       <c r="J36" s="3">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>59</v>
+        <v>171</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="I37" s="3" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="J37" s="3">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>59</v>
+        <v>171</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>59</v>
+        <v>171</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="J38" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>177</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
@@ -3359,45 +3391,45 @@
         <v>179</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>180</v>
+        <v>112</v>
       </c>
       <c r="J39" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>182</v>
+        <v>58</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J40" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>184</v>
@@ -3406,440 +3438,440 @@
         <v>185</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>186</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="J41" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="D42" s="3" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="J42" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>193</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="J44" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>44</v>
+        <v>200</v>
       </c>
       <c r="J45" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>71</v>
+        <v>190</v>
       </c>
       <c r="J46" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>180</v>
+        <v>43</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>59</v>
+        <v>216</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="J51" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>37</v>
+        <v>223</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>222</v>
+        <v>71</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>225</v>
+        <v>58</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="J55" s="3">
         <v>2</v>
@@ -3847,29 +3879,29 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>130</v>
+        <v>231</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="J56" s="3">
         <v>0</v>
@@ -3877,329 +3909,329 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>182</v>
+        <v>237</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>59</v>
+        <v>238</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>232</v>
+        <v>156</v>
       </c>
       <c r="J57" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="J58" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>130</v>
+        <v>242</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>59</v>
+        <v>216</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="J59" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>72</v>
+        <v>245</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>185</v>
+        <v>247</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J60" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>72</v>
+        <v>249</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>59</v>
+        <v>238</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="J61" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>242</v>
+        <v>133</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J62" s="3">
         <v>23</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J62" s="3">
-        <v>25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J63" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="J64" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>251</v>
+        <v>133</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>253</v>
+        <v>210</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>215</v>
+        <v>58</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="J65" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>72</v>
+        <v>261</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>48</v>
+        <v>264</v>
       </c>
       <c r="J66" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>248</v>
+        <v>133</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>48</v>
+        <v>190</v>
       </c>
       <c r="J67" s="3">
         <v>1</v>
@@ -4207,991 +4239,989 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>59</v>
+        <v>238</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="J68" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>72</v>
+        <v>269</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="J69" s="3">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>263</v>
+        <v>133</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="J70" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>180</v>
+        <v>43</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="J73" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="J74" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>232</v>
+        <v>43</v>
       </c>
       <c r="J75" s="3">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="J76" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>286</v>
+        <v>100</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>196</v>
+        <v>43</v>
       </c>
       <c r="J77" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>185</v>
+        <v>298</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>248</v>
+        <v>301</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>217</v>
+        <v>305</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>294</v>
+        <v>196</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J80" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>130</v>
+        <v>307</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J81" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>299</v>
+        <v>212</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="J82" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>303</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>180</v>
+        <v>264</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>307</v>
+        <v>196</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>232</v>
+        <v>47</v>
       </c>
       <c r="J84" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="J85" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>130</v>
+        <v>304</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>45</v>
+        <v>321</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>314</v>
+        <v>281</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>59</v>
+        <v>216</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>130</v>
+        <v>323</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>59</v>
+        <v>238</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>122</v>
+        <v>274</v>
       </c>
       <c r="J88" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>130</v>
+        <v>326</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J89" s="3">
         <v>23</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J89" s="3">
-        <v>25</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>319</v>
+        <v>133</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="J90" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>322</v>
+        <v>133</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>275</v>
+        <v>210</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="J91" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>217</v>
+        <v>334</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J92" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="J93" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>200</v>
+        <v>344</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J95" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>335</v>
+        <v>187</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>336</v>
+        <v>196</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>266</v>
+        <v>190</v>
       </c>
       <c r="J96" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>339</v>
+        <v>281</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>340</v>
+        <v>215</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>136</v>
+        <v>216</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>341</v>
+        <v>67</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>48</v>
+        <v>225</v>
       </c>
       <c r="J97" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>244</v>
+        <v>196</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="J98" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>185</v>
+        <v>352</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>180</v>
+        <v>264</v>
       </c>
       <c r="J99" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>185</v>
+        <v>352</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -5199,29 +5229,29 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>189</v>
+        <v>359</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="J101" s="3">
         <v>0</v>
@@ -5229,59 +5259,59 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>355</v>
+        <v>319</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>356</v>
+        <v>185</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="J102" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>360</v>
+        <v>185</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>48</v>
+        <v>190</v>
       </c>
       <c r="J103" s="3">
         <v>1</v>
@@ -5289,89 +5319,89 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>363</v>
+        <v>281</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>200</v>
+        <v>367</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>180</v>
+        <v>47</v>
       </c>
       <c r="J104" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>200</v>
+        <v>371</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J105" s="3">
         <v>23</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J105" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>130</v>
+        <v>373</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="J106" s="3">
         <v>0</v>
@@ -5379,216 +5409,246 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="J107" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>275</v>
+        <v>338</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="J108" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>196</v>
+        <v>300</v>
       </c>
       <c r="J109" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>236</v>
+        <v>331</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J110" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>275</v>
+        <v>196</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>266</v>
+        <v>200</v>
       </c>
       <c r="J111" s="3">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>386</v>
+        <v>338</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>387</v>
+        <v>139</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="J112" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>59</v>
+        <v>223</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>44</v>
+        <v>200</v>
       </c>
       <c r="J113" s="3">
-        <v>25</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J114" s="3">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J113"/>
+  <autoFilter ref="A1:J114"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5702,6 +5762,7 @@
     <hyperlink ref="H111" r:id="rId110"/>
     <hyperlink ref="H112" r:id="rId111"/>
     <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5709,9 +5770,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="49" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5720,36 +5781,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5757,410 +5818,182 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>179</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>130</v>
+        <v>249</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>209</v>
+        <v>267</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>210</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>130</v>
+        <v>354</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>188</v>
+        <v>355</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>214</v>
+        <v>352</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>216</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>130</v>
+        <v>357</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>217</v>
+        <v>358</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>178</v>
+        <v>359</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>218</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>219</v>
+        <v>361</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>220</v>
+        <v>319</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>221</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>130</v>
+        <v>373</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>227</v>
+        <v>355</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>228</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>130</v>
+        <v>375</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>267</v>
+        <v>376</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>268</v>
+        <v>210</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G23"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6172,18 +6005,6 @@
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
-    <hyperlink ref="G22" r:id="rId21"/>
-    <hyperlink ref="G23" r:id="rId22"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6197,15 +6018,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B2" s="3">
         <v>25</v>
@@ -6213,39 +6034,39 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>303</v>
+        <v>405</v>
       </c>
       <c r="B7" s="3">
         <v>18</v>
@@ -6253,23 +6074,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B10" s="3">
         <v>13</v>
@@ -6277,7 +6098,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -6285,42 +6106,42 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6330,29 +6151,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
         <v>6</v>
@@ -6360,23 +6181,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>67</v>
+        <v>281</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6384,7 +6205,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>188</v>
+        <v>105</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6392,7 +6213,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -6400,15 +6221,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>57</v>
+        <v>212</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6416,7 +6237,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6424,7 +6245,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6432,7 +6253,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6440,7 +6261,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6448,7 +6269,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6456,10 +6277,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>331</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6470,23 +6291,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2">
@@ -6494,13 +6315,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" s="3">
-        <v>22.5</v>
+        <v>31.4</v>
       </c>
       <c r="D2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -6508,13 +6329,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="C3" s="3">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="D3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -6522,13 +6343,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3">
-        <v>14.0</v>
+        <v>17.3</v>
       </c>
       <c r="D4" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -6536,7 +6357,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C5" s="3">
         <v>11.2</v>
@@ -6550,7 +6371,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3">
         <v>10.9</v>
@@ -6564,7 +6385,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="3">
         <v>7.0</v>
@@ -6578,7 +6399,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C8" s="3">
         <v>6.2</v>
@@ -6592,7 +6413,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C9" s="3">
         <v>5.8</v>
@@ -6606,13 +6427,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>188</v>
+        <v>281</v>
       </c>
       <c r="C10" s="3">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -6620,10 +6441,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
@@ -6634,13 +6455,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -6648,13 +6469,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="C13" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6662,10 +6483,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C14" s="3">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -6676,13 +6497,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -6690,7 +6511,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6713,46 +6534,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>341</v>
+        <v>419</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>12</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -6768,71 +6589,71 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="3">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>225</v>
+        <v>171</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>127</v>
+        <v>223</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>387</v>
+        <v>130</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6859,34 +6680,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -6894,31 +6715,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -6926,31 +6747,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>343</v>
+        <v>430</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>344</v>
+        <v>431</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F3" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>345</v>
+        <v>433</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>196</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -6958,31 +6779,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>386</v>
+        <v>222</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="F4" s="3">
         <v>74</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5">
@@ -6990,31 +6811,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="F5" s="3">
         <v>74</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6">
@@ -7022,31 +6843,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="F6" s="3">
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
     </row>
     <row r="7">
@@ -7054,31 +6875,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="F7" s="3">
         <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -7086,31 +6907,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="F8" s="3">
         <v>54</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -7118,31 +6939,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>253</v>
+        <v>215</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="F9" s="3">
         <v>52</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10">
@@ -7150,31 +6971,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>421</v>
+        <v>463</v>
       </c>
       <c r="F10" s="3">
         <v>52</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -7182,31 +7003,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>149</v>
+        <v>466</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>44</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -7214,31 +7035,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>456</v>
+        <v>152</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="F12" s="3">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>433</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -7246,31 +7067,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F13" s="3">
+        <v>47</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>444</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="F13" s="3">
-        <v>44</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -7278,31 +7099,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="F14" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>465</v>
+        <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>153</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15">
@@ -7310,31 +7131,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>351</v>
+        <v>478</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>181</v>
+        <v>455</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>294</v>
+        <v>210</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F15" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>196</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
@@ -7342,31 +7163,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>351</v>
+        <v>430</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F16" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>232</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17">
@@ -7374,31 +7195,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>189</v>
+        <v>485</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>487</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>476</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18">
@@ -7406,31 +7227,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>275</v>
+        <v>196</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>418</v>
+        <v>463</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>481</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
@@ -7438,31 +7259,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="F19" s="3">
+        <v>32</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="F19" s="3">
-        <v>27</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -7470,31 +7291,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>486</v>
+        <v>363</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>188</v>
+        <v>497</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>425</v>
+        <v>463</v>
       </c>
       <c r="F20" s="3">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
     </row>
     <row r="21">
@@ -7502,31 +7323,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>489</v>
+        <v>77</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="F21" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>105</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W24.xlsx
+++ b/reports/devops-jobs-israel-2026-W24.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="518">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-10T10:18:17</t>
+    <t xml:space="preserve">2026-06-11T10:54:21</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,12 +57,15 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
+    <t xml:space="preserve">0.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary disclosure rate %</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.0%</t>
   </si>
   <si>
-    <t xml:space="preserve">Salary disclosure rate %</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maintained by</t>
   </si>
   <si>
@@ -156,21 +159,24 @@
     <t xml:space="preserve">Cloud Architect</t>
   </si>
   <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4855504101?gh_jid=4855504101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Architect</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure, Networking, Security, AI/MLOps</t>
   </si>
   <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4888525101?gh_jid=4888525101</t>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4883675101?gh_jid=4883675101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4883675101?gh_jid=4883675101</t>
-  </si>
-  <si>
     <t xml:space="preserve">Solution Architect</t>
   </si>
   <si>
@@ -306,21 +312,6 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
   </si>
   <si>
-    <t xml:space="preserve">R&amp;D Team Leader, AI-Native - JFrog Fly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7388234&amp;gh_jid=7388234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Nginx, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7598823&amp;gh_jid=7598823</t>
-  </si>
-  <si>
     <t xml:space="preserve">Site Reliability Engineer</t>
   </si>
   <si>
@@ -333,19 +324,16 @@
     <t xml:space="preserve">2026-06-10</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gongio</t>
   </si>
   <si>
     <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
   </si>
   <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668079006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
   </si>
   <si>
     <t xml:space="preserve">Senior Director of Platform Security</t>
@@ -432,21 +420,60 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer (Remote)</t>
+    <t xml:space="preserve">DevOps Engineer (Austin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austin, Texas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5710946004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Boston)</t>
   </si>
   <si>
     <t xml:space="preserve">Boston, Massachusetts, United States</t>
   </si>
   <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Security, Argo CD, Observability</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010968004</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Engineer (New York)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010964004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Rhode Island)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providence, Rhode Island, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010965004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Washington)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Washington, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010969004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Data Platform Engineer</t>
   </si>
   <si>
@@ -489,9 +516,6 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
     <t xml:space="preserve">DevSecOps</t>
   </si>
   <si>
@@ -510,1021 +534,991 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
   </si>
   <si>
-    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stampli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-stampli-4427173588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-abra-4425003795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4422246034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4425198243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zafran Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4423379202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4426065244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Administrator &amp; DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appdome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-administrator-devops-at-appdome-4421928922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudBuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cloudbuzz-4374206449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4425654229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest acq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-acq-4427190837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VoIP/DevOps Engineer (SIP Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Squaretalk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/voip-devops-engineer-sip-focus-at-squaretalk-4426348262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4414190903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CorrActions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-devops-engineer-at-corractions-4423612672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4427141543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentee Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-mentee-robotics-4422793922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4421593110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4406062787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-27</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-abra-4425003795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4422246034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4425198243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Administrator &amp; DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appdome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-administrator-devops-at-appdome-4421928922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zafran Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4423379202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4425654229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4425242600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
+    <t xml:space="preserve">Nogamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4427161800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4427156928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bynet-data-communications-4423131095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22765 - Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22765-reliability-engineer-sre-at-qualitest-4420738290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeva Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mastercard</t>
   </si>
   <si>
     <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural Intelligence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4414190903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizon Technologies LTD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-horizon-technologies-ltd-4423126060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hof HaCarmel Regional Council, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4422250329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36354)</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-mastercard-4421916027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagomi Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-nagomi-security-4425014911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-millennium-4425034300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lenovo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-lenovo-4424600261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-quanthealth-4425994726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vi-4421931598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-engineer-at-intel-4424414559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfraEdge IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infraedge-il-4421944139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SailPoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sola Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sola-security-4425029092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-quantum-machines-4412371822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-ai-4422235857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tekgence Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4426102112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4425543714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triarii Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-triarii-research-4423621466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4427054576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4425076264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4425237881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-extreme-4426777242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-elbit-systems-israel-4421911706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Squad Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-squad-leader-at-milestone-systems-4427508430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-commit-4425110784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-youcc-technologies-ltd-4421927527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4422797374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ur-tech-jobs-4425565373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Infrastructure Engineer（SRE）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">株式会社GA technologies / GA technologies Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-infrastructure-engineer%EF%BC%88sre%EF%BC%89-at-%E6%A0%AA%E5%BC%8F%E4%BC%9A%E7%A4%BEga-technologies-ga-technologies-co-ltd-4425654538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (U.S Citizen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIGO Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-u-s-citizen-at-oligo-security-4427007687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-platform-engineer-at-gotfriends-4421571443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetNut.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-tech-lead-at-f5-4426768847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grafana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortinet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fortinet-4393535304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sojo Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-engineer-student-position-at-sojo-industries-4423100988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4405103757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
   </si>
   <si>
     <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36354-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4425486507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sola Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sola-security-4425029092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VoIP/DevOps Engineer (SIP Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Squaretalk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/voip-devops-engineer-sip-focus-at-squaretalk-4426348262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-commit-4425110784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfraEdge IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infraedge-il-4421944139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-engineer-at-intel-4424414559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paz - yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yaqum, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-paz-yellow-4425456877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4426710226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SailPoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vi-4421931598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4425603835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ur-tech-jobs-4425565373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-quantum-machines-4412371822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-youcc-technologies-ltd-4421927527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22765 - Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22765-reliability-engineer-sre-at-qualitest-4420738290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-viz-ai-4405964696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeva Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mastercard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-mastercard-4421916027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagomi Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-nagomi-security-4425014911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-millennium-4425034300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lenovo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-lenovo-4424600261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-comblack-4421694778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Private Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4414601125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4421926577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4421593110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Infrastructure Engineer（SRE）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">株式会社GA technologies / GA technologies Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-infrastructure-engineer%EF%BC%88sre%EF%BC%89-at-%E6%A0%AA%E5%BC%8F%E4%BC%9A%E7%A4%BEga-technologies-ga-technologies-co-ltd-4425654538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roboteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-roboteam-4419684684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4425543714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Time Group - Software Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-real-time-group-software-solutions-4421942748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-ai-4422235857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer - 236606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-236606-at-experis-israel-4422794863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (LCM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-lcm-at-extreme-4426742604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-infrastructure-engineer-at-comblack-4425497939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4421930625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-elbit-systems-israel-4421911706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4422797374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-quanthealth-4425994726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-platform-engineer-at-gotfriends-4421571443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-lead-at-akamai-technologies-4422930991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NetNut.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4420191774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grafana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-cato-networks-4398801612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Docker, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remoteok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-support-engineer-level-1132895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aristocrat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4425582424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1539,10 +1533,10 @@
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
@@ -1703,7 +1697,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">
@@ -1711,7 +1705,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -1719,7 +1713,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -1727,7 +1721,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>542</v>
+        <v>565</v>
       </c>
     </row>
     <row r="10">
@@ -1735,7 +1729,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1751,7 +1745,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -1760,26 +1754,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1788,26 +1782,26 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1823,41 +1817,49 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="B5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B6" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1874,130 +1876,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B2" s="3">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B3" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>406</v>
+        <v>502</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>504</v>
+        <v>402</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>507</v>
+        <v>406</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>411</v>
+        <v>506</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>404</v>
+        <v>507</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>509</v>
+        <v>400</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2016,54 +2018,54 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3">
-        <v>13.3</v>
+        <v>15.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3">
-        <v>43.0</v>
+        <v>35.3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -2072,67 +2074,67 @@
         <v>8.3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>29.8</v>
+        <v>34.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>20.1</v>
+        <v>17.7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.5</v>
+        <v>23.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2145,7 +2147,7 @@
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
     <col min="2" max="2" width="49" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2157,130 +2159,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -2288,572 +2290,572 @@
         <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="J6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J9" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J10" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J16" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J18" s="3">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="J19" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="J21" s="3">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J22" s="3">
         <v>13</v>
@@ -2861,258 +2863,258 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="J23" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="J24" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="J27" s="3">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="J28" s="3">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="J29" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>146</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="J30" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3120,31 +3122,31 @@
         <v>147</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H31" s="3" t="s">
+      <c r="I31" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="I31" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="J31" s="3">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -3158,57 +3160,57 @@
         <v>153</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>154</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>155</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="C33" s="3" t="s">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>158</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>159</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
@@ -3216,332 +3218,336 @@
         <v>160</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="J34" s="3">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F35" s="3"/>
+        <v>69</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="G35" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>165</v>
+        <v>41</v>
       </c>
       <c r="J35" s="3">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J36" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>171</v>
+        <v>60</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="G37" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J37" s="3">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="J38" s="3">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>178</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>179</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>112</v>
+        <v>180</v>
       </c>
       <c r="J39" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F40" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>183</v>
+      </c>
       <c r="G40" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="J40" s="3">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>185</v>
+        <v>60</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="J41" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>47</v>
+        <v>150</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>194</v>
+        <v>129</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>47</v>
+        <v>199</v>
       </c>
       <c r="J44" s="3">
         <v>2</v>
@@ -3549,209 +3555,209 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="J45" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>201</v>
+        <v>129</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="J46" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>171</v>
+        <v>60</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>133</v>
+        <v>208</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J48" s="3">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>133</v>
+        <v>213</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J51" s="3">
         <v>0</v>
@@ -3759,29 +3765,29 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>133</v>
+        <v>221</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>1</v>
@@ -3789,89 +3795,89 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>220</v>
+        <v>129</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>223</v>
+        <v>37</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="J53" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="D55" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>47</v>
+        <v>199</v>
       </c>
       <c r="J55" s="3">
         <v>2</v>
@@ -3879,179 +3885,179 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>171</v>
+        <v>219</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>103</v>
+        <v>236</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>238</v>
+        <v>135</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="J57" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>133</v>
+        <v>241</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>185</v>
+        <v>243</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>139</v>
+        <v>244</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>216</v>
+        <v>60</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="J59" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>139</v>
+        <v>252</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>47</v>
+        <v>236</v>
       </c>
       <c r="J60" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>249</v>
+        <v>171</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>238</v>
+        <v>60</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -4059,209 +4065,209 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="J62" s="3">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J63" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>165</v>
+        <v>262</v>
       </c>
       <c r="J64" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="J65" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>264</v>
+        <v>104</v>
       </c>
       <c r="J66" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>133</v>
+        <v>268</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>190</v>
+        <v>271</v>
       </c>
       <c r="J67" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>238</v>
+        <v>135</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J68" s="3">
         <v>0</v>
@@ -4269,359 +4275,359 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>225</v>
+        <v>104</v>
       </c>
       <c r="J69" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>274</v>
+        <v>104</v>
       </c>
       <c r="J70" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>43</v>
+        <v>281</v>
       </c>
       <c r="J71" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>185</v>
+        <v>243</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>139</v>
+        <v>244</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>47</v>
+        <v>205</v>
       </c>
       <c r="J72" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>282</v>
+        <v>190</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>47</v>
+        <v>236</v>
       </c>
       <c r="J73" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>284</v>
+        <v>97</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>237</v>
+        <v>289</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>238</v>
+        <v>60</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>200</v>
+        <v>44</v>
       </c>
       <c r="J74" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>196</v>
+        <v>293</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="J75" s="3">
         <v>22</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J75" s="3">
-        <v>26</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>196</v>
+        <v>298</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>225</v>
+        <v>51</v>
       </c>
       <c r="J76" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J77" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>298</v>
+        <v>190</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>300</v>
+        <v>51</v>
       </c>
       <c r="J78" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J79" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>47</v>
+        <v>199</v>
       </c>
       <c r="J80" s="3">
         <v>2</v>
@@ -4629,119 +4635,119 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>307</v>
+        <v>274</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="J81" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>310</v>
+        <v>129</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>212</v>
+        <v>312</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>225</v>
+        <v>51</v>
       </c>
       <c r="J82" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>196</v>
+        <v>251</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>58</v>
+        <v>252</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>264</v>
+        <v>205</v>
       </c>
       <c r="J83" s="3">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>304</v>
+        <v>129</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>47</v>
+        <v>199</v>
       </c>
       <c r="J84" s="3">
         <v>2</v>
@@ -4749,479 +4755,479 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>304</v>
+        <v>129</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="J85" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>304</v>
+        <v>129</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="J86" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>281</v>
+        <v>324</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>215</v>
+        <v>325</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>216</v>
+        <v>135</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="J87" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>323</v>
+        <v>73</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>238</v>
+        <v>60</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>274</v>
+        <v>51</v>
       </c>
       <c r="J88" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>326</v>
+        <v>129</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>294</v>
+        <v>190</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="J89" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>207</v>
+        <v>325</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J90" s="3">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>133</v>
+        <v>332</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>331</v>
+        <v>196</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>156</v>
+        <v>199</v>
       </c>
       <c r="J91" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="J92" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>337</v>
+        <v>225</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>338</v>
+        <v>229</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>70</v>
+        <v>199</v>
       </c>
       <c r="J93" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="D94" s="3" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>341</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="J94" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>343</v>
+        <v>214</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>344</v>
+        <v>190</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="J95" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>187</v>
+        <v>344</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>196</v>
+        <v>345</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>67</v>
+        <v>346</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>190</v>
+        <v>51</v>
       </c>
       <c r="J96" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>281</v>
+        <v>349</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>216</v>
+        <v>60</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="J97" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>196</v>
+        <v>353</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="J98" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>351</v>
+        <v>250</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>264</v>
+        <v>51</v>
       </c>
       <c r="J99" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -5229,209 +5235,209 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>359</v>
+        <v>243</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>139</v>
+        <v>244</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="J101" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>319</v>
+        <v>365</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>103</v>
+        <v>262</v>
       </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>190</v>
+        <v>51</v>
       </c>
       <c r="J103" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>281</v>
+        <v>371</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>367</v>
+        <v>229</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="J104" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>369</v>
+        <v>171</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>371</v>
+        <v>243</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>139</v>
+        <v>244</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J105" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="J106" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J107" s="3">
         <v>0</v>
@@ -5439,216 +5445,126 @@
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>338</v>
+        <v>190</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="J108" s="3">
         <v>22</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J108" s="3">
-        <v>6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>382</v>
+        <v>256</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="J109" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>331</v>
+        <v>387</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>210</v>
+        <v>388</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>156</v>
+        <v>262</v>
       </c>
       <c r="J110" s="3">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="J111" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="I112" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="J112" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="I113" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="J113" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="I114" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J114" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J114"/>
+  <autoFilter ref="A1:J111"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5760,9 +5676,6 @@
     <hyperlink ref="H109" r:id="rId108"/>
     <hyperlink ref="H110" r:id="rId109"/>
     <hyperlink ref="H111" r:id="rId110"/>
-    <hyperlink ref="H112" r:id="rId111"/>
-    <hyperlink ref="H113" r:id="rId112"/>
-    <hyperlink ref="H114" r:id="rId113"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5770,9 +5683,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5781,219 +5694,466 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>214</v>
+        <v>130</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>215</v>
+        <v>142</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>217</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>231</v>
+        <v>144</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>232</v>
+        <v>130</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>233</v>
+        <v>145</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>234</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>249</v>
+        <v>188</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>250</v>
+        <v>189</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>251</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>267</v>
+        <v>206</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>268</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>354</v>
+        <v>129</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>355</v>
+        <v>211</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>352</v>
+        <v>194</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>356</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>357</v>
+        <v>216</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>358</v>
+        <v>217</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>359</v>
+        <v>218</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>360</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>361</v>
+        <v>227</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>319</v>
+        <v>228</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>362</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>373</v>
+        <v>237</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>355</v>
+        <v>238</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>374</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>375</v>
+        <v>241</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>376</v>
+        <v>242</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>210</v>
+        <v>243</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>377</v>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G24"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6005,6 +6165,19 @@
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
+    <hyperlink ref="G22" r:id="rId21"/>
+    <hyperlink ref="G23" r:id="rId22"/>
+    <hyperlink ref="G24" r:id="rId23"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6018,103 +6191,103 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>405</v>
+        <v>183</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>178</v>
+        <v>400</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
@@ -6122,7 +6295,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B14" s="3">
         <v>9</v>
@@ -6130,7 +6303,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6138,7 +6311,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
@@ -6151,29 +6324,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="B3" s="3">
         <v>6</v>
@@ -6181,15 +6354,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>281</v>
+        <v>161</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6197,7 +6370,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6205,7 +6378,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6213,23 +6386,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>184</v>
+        <v>58</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>212</v>
+        <v>118</v>
       </c>
       <c r="B9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6237,7 +6410,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>122</v>
+        <v>196</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6245,7 +6418,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>134</v>
+        <v>214</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6253,7 +6426,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>170</v>
+        <v>225</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6261,7 +6434,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>187</v>
+        <v>250</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6269,7 +6442,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>319</v>
+        <v>256</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6277,7 +6450,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6298,16 +6471,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2">
@@ -6315,13 +6488,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C2" s="3">
-        <v>31.4</v>
+        <v>22.7</v>
       </c>
       <c r="D2" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -6329,13 +6502,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>152</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3">
-        <v>17.5</v>
+        <v>19.4</v>
       </c>
       <c r="D3" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -6343,7 +6516,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="C4" s="3">
         <v>17.3</v>
@@ -6357,13 +6530,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="C5" s="3">
-        <v>11.2</v>
+        <v>14.0</v>
       </c>
       <c r="D5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -6371,10 +6544,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="C6" s="3">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -6385,13 +6558,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C7" s="3">
-        <v>7.0</v>
+        <v>10.9</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -6399,10 +6572,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3">
-        <v>6.2</v>
+        <v>7.0</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -6413,10 +6586,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="C9" s="3">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -6427,13 +6600,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>281</v>
+        <v>175</v>
       </c>
       <c r="C10" s="3">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="D10" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -6441,13 +6614,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="C11" s="3">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6455,13 +6628,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="C12" s="3">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6469,13 +6642,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6483,10 +6656,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -6497,13 +6670,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>143</v>
+        <v>196</v>
       </c>
       <c r="C15" s="3">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -6511,7 +6684,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6534,46 +6707,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>419</v>
+        <v>346</v>
       </c>
       <c r="B2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>420</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="3">
         <v>67</v>
       </c>
-      <c r="B3" s="3">
-        <v>70</v>
-      </c>
       <c r="C3" s="3" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -6589,63 +6762,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B2" s="3">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>238</v>
+        <v>176</v>
       </c>
       <c r="B6" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>171</v>
+        <v>219</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -6653,7 +6826,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6668,7 +6841,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6680,34 +6853,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -6715,31 +6888,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -6747,31 +6920,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="F3" s="3">
+        <v>74</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="F3" s="3">
-        <v>88</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>433</v>
-      </c>
       <c r="J3" s="3" t="s">
-        <v>120</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4">
@@ -6779,31 +6952,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="F4" s="3">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>439</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -6811,31 +6984,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="F5" s="3">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="6">
@@ -6843,31 +7016,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F6" s="3">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>439</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -6875,31 +7048,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>450</v>
+        <v>161</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>451</v>
+        <v>420</v>
       </c>
       <c r="F7" s="3">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -6907,31 +7080,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>210</v>
+        <v>449</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="F8" s="3">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>444</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -6939,31 +7112,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>243</v>
+        <v>453</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="F9" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>439</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -6971,31 +7144,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>192</v>
+        <v>243</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="F10" s="3">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>70</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11">
@@ -7003,31 +7176,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="F11" s="3">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>200</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12">
@@ -7035,31 +7208,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>152</v>
+        <v>464</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -7067,31 +7240,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>196</v>
+        <v>298</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>469</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>444</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -7099,31 +7272,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="F14" s="3">
+        <v>32</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="F14" s="3">
-        <v>47</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>477</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15">
@@ -7131,31 +7304,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>478</v>
+        <v>444</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>455</v>
+        <v>79</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>43</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16">
@@ -7163,31 +7336,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>430</v>
+        <v>477</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>481</v>
+        <v>118</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>210</v>
+        <v>478</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="F16" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>120</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17">
@@ -7195,31 +7368,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F17" s="3">
+        <v>30</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="F17" s="3">
-        <v>40</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>488</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>156</v>
+        <v>438</v>
       </c>
     </row>
     <row r="18">
@@ -7227,31 +7400,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>490</v>
+        <v>352</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="F18" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>43</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19">
@@ -7259,31 +7432,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>493</v>
+        <v>447</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>463</v>
+        <v>420</v>
       </c>
       <c r="F19" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>200</v>
+        <v>492</v>
       </c>
     </row>
     <row r="20">
@@ -7291,31 +7464,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>363</v>
+        <v>493</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>497</v>
+        <v>193</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>463</v>
+        <v>425</v>
       </c>
       <c r="F20" s="3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>225</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -7323,31 +7496,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>440</v>
+        <v>471</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>77</v>
+        <v>496</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>78</v>
+        <v>353</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="F21" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W24.xlsx
+++ b/reports/devops-jobs-israel-2026-W24.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="542">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-11T10:54:21</t>
+    <t xml:space="preserve">2026-06-12T10:37:26</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9%</t>
+    <t xml:space="preserve">0.8%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -312,277 +312,961 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
   </si>
   <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Architect - DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Austin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austin, Texas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5710946004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Boston)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boston, Massachusetts, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010968004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (New York)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010964004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Rhode Island)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providence, Rhode Island, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010965004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Washington)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Washington, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010969004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud Group Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-abra-4425003795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4422246034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4425198243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest acq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-acq-4427190837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4425654229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Administrator &amp; DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appdome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-administrator-devops-at-appdome-4421928922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4426065244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aman Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aman-group-4423678087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VoIP/DevOps Engineer (SIP Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Squaretalk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/voip-devops-engineer-sip-focus-at-squaretalk-4426348262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4427161800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ata, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4395474406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-quanthealth-4425994726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-quantum-machines-4412371822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-coralogix-4368406182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfraEdge IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infraedge-il-4421944139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paz - yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yaqum, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-paz-yellow-4425456877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4427156928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vi-4421931598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sola Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sola-security-4425029092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bynet-data-communications-4423131095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Automation &amp; Release Engineering Specialist (25103)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-automation-release-engineering-specialist-25103-at-yael-group-4424811001</t>
+  </si>
+  <si>
     <t xml:space="preserve">Site Reliability Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Linux, Python, Prometheus, Grafana, New Relic, Networking, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7957880&amp;gh_jid=7957880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Architect - DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Austin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austin, Texas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5710946004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Boston)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston, Massachusetts, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010968004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (New York)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010964004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Rhode Island)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Providence, Rhode Island, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010965004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Washington)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Washington, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010969004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraud Group Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeva Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mastercard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-mastercard-4421916027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Infrastructure Engineer（SRE）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">株式会社GA technologies / GA technologies Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-infrastructure-engineer%EF%BC%88sre%EF%BC%89-at-%E6%A0%AA%E5%BC%8F%E4%BC%9A%E7%A4%BEga-technologies-ga-technologies-co-ltd-4425654538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4427516055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentee Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-mentee-robotics-4422793922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagomi Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-nagomi-security-4425014911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lenovo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-lenovo-4424600261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CorrActions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-devops-engineer-at-corractions-4423612672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer (Compute Runtime)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CyberArk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-compute-runtime-at-cyberark-4405971728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (25078)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25078-at-yael-group-4423652623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4427054576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Azure DevOps &amp; Release Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-azure-devops-release-engineer-at-abra-4426234726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4421593110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-logica-it-4423649420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4421926577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-ai-4422235857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tekgence Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4426102112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4425543714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4425076264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4425237881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer - 236606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-236606-at-experis-israel-4422794863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-elbit-systems-israel-4421911706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-extreme-4426777242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHY System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-infrastructure-engineer-at-comblack-4425497939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Squad Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-squad-leader-at-milestone-systems-4427508430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-commit-4425110784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Hai, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ur-tech-jobs-4425565373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (U.S Citizen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIGO Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-u-s-citizen-at-oligo-security-4427007687</t>
   </si>
   <si>
     <t xml:space="preserve">Devops Manager</t>
@@ -591,766 +1275,169 @@
     <t xml:space="preserve">Stampli</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-stampli-4427173588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-abra-4425003795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4422246034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4425198243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zafran Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4423379202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4426065244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Administrator &amp; DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appdome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-administrator-devops-at-appdome-4421928922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudBuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cloudbuzz-4374206449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4425654229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest acq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-acq-4427190837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VoIP/DevOps Engineer (SIP Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Squaretalk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/voip-devops-engineer-sip-focus-at-squaretalk-4426348262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4414190903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CorrActions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-devops-engineer-at-corractions-4423612672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural Intelligence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4427141543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentee Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-mentee-robotics-4422793922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4421593110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4406062787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4427161800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4427156928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bynet-data-communications-4423131095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22765 - Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/22765-reliability-engineer-sre-at-qualitest-4420738290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeva Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mastercard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-mastercard-4421916027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagomi Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-nagomi-security-4425014911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-millennium-4425034300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lenovo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-lenovo-4424600261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-quanthealth-4425994726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vi-4421931598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Engineer</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-stampli-4427522493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-platform-engineer-at-gotfriends-4421571443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT / Cloud Specialist - 235226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-cloud-specialist-235226-at-experis-israel-4423620429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortinet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fortinet-4393535304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
   </si>
   <si>
     <t xml:space="preserve">Intel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-engineer-at-intel-4424414559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfraEdge IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infraedge-il-4421944139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SailPoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sola Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sola-security-4425029092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-quantum-machines-4412371822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-ai-4422235857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tekgence Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4426102112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4425543714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Triarii Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-triarii-research-4423621466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4427054576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4425076264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4425237881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-extreme-4426777242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-elbit-systems-israel-4421911706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Squad Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-squad-leader-at-milestone-systems-4427508430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-commit-4425110784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-youcc-technologies-ltd-4421927527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4422797374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ur-tech-jobs-4425565373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Infrastructure Engineer（SRE）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">株式会社GA technologies / GA technologies Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-infrastructure-engineer%EF%BC%88sre%EF%BC%89-at-%E6%A0%AA%E5%BC%8F%E4%BC%9A%E7%A4%BEga-technologies-ga-technologies-co-ltd-4425654538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (U.S Citizen)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLIGO Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-u-s-citizen-at-oligo-security-4427007687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-platform-engineer-at-gotfriends-4421571443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NetNut.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-team-lead-at-netnut-io-4414460565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-tech-lead-at-f5-4426768847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grafana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fortinet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fortinet-4393535304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
   </si>
   <si>
     <t xml:space="preserve">IT Specialist</t>
@@ -1362,6 +1449,18 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
     <t xml:space="preserve">Support Engineer</t>
   </si>
   <si>
@@ -1377,6 +1476,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Infrastructure &amp; Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Squadron Israel - Hatayeset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-technical-support-specialist-at-the-squadron-israel-hatayeset-4421938671</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Support Specialist - Temporary position</t>
   </si>
   <si>
@@ -1410,40 +1524,22 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sojo Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-engineer-student-position-at-sojo-industries-4423100988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-comblack-4425486490</t>
   </si>
   <si>
     <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
@@ -1470,9 +1566,6 @@
     <t xml:space="preserve">Innoviz Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
   </si>
   <si>
@@ -1488,34 +1581,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
   </si>
   <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4405103757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4425582424</t>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
@@ -1528,9 +1603,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
@@ -1697,7 +1769,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -1705,7 +1777,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1713,7 +1785,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -1721,7 +1793,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>565</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10">
@@ -1793,7 +1865,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
@@ -1820,44 +1892,44 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="B2" s="3">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>425</v>
+        <v>470</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1876,87 +1948,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>500</v>
+        <v>525</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>501</v>
+        <v>526</v>
       </c>
       <c r="B2" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>503</v>
+        <v>428</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>504</v>
+        <v>528</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>406</v>
+        <v>529</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>505</v>
+        <v>432</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>506</v>
+        <v>530</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>507</v>
+        <v>531</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -1964,7 +2036,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -1972,7 +2044,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
@@ -1980,15 +2052,15 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>396</v>
+        <v>349</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>508</v>
+        <v>532</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -1996,7 +2068,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
@@ -2024,13 +2096,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>511</v>
+        <v>535</v>
       </c>
     </row>
     <row r="2">
@@ -2038,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3">
-        <v>15.0</v>
+        <v>17.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2053,19 +2125,19 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C3" s="3">
-        <v>35.3</v>
+        <v>38.3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>513</v>
+        <v>537</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -2074,67 +2146,67 @@
         <v>8.3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>514</v>
+        <v>538</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>515</v>
+        <v>539</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.9</v>
+        <v>30.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>516</v>
+        <v>540</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>517</v>
+        <v>541</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>23.3</v>
+        <v>13.9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2145,7 +2217,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="49" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -2218,7 +2290,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -2250,7 +2322,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -2282,7 +2354,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -2314,7 +2386,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2346,7 +2418,7 @@
         <v>51</v>
       </c>
       <c r="J6" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2378,7 +2450,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -2410,7 +2482,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -2442,7 +2514,7 @@
         <v>66</v>
       </c>
       <c r="J9" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -2474,7 +2546,7 @@
         <v>72</v>
       </c>
       <c r="J10" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -2506,7 +2578,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -2538,7 +2610,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -2570,7 +2642,7 @@
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -2602,7 +2674,7 @@
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -2634,7 +2706,7 @@
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -2666,7 +2738,7 @@
         <v>92</v>
       </c>
       <c r="J16" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2698,24 +2770,24 @@
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="C18" s="3" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>98</v>
@@ -2735,10 +2807,10 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>60</v>
@@ -2762,7 +2834,7 @@
         <v>104</v>
       </c>
       <c r="J19" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -2770,7 +2842,7 @@
         <v>105</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>60</v>
@@ -2791,21 +2863,21 @@
         <v>107</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="J20" s="3">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>60</v>
@@ -2823,59 +2895,59 @@
         <v>111</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="J21" s="3">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J22" s="3">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>119</v>
@@ -2887,24 +2959,24 @@
         <v>120</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="J23" s="3">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="D24" s="3" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>38</v>
@@ -2919,27 +2991,27 @@
         <v>124</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>127</v>
@@ -2954,7 +3026,7 @@
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
@@ -2962,231 +3034,231 @@
         <v>129</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="J26" s="3">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="J27" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="D28" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J28" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="J30" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>148</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J31" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>59</v>
@@ -3198,30 +3270,30 @@
         <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>60</v>
@@ -3230,30 +3302,30 @@
         <v>38</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J34" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>60</v>
@@ -3262,30 +3334,30 @@
         <v>69</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J35" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>60</v>
@@ -3294,30 +3366,30 @@
         <v>69</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J36" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>60</v>
@@ -3326,33 +3398,33 @@
         <v>38</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J37" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="D38" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>69</v>
@@ -3362,27 +3434,27 @@
         <v>24</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J38" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>38</v>
@@ -3392,21 +3464,21 @@
         <v>24</v>
       </c>
       <c r="H39" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="I39" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="J39" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>60</v>
@@ -3418,27 +3490,27 @@
         <v>38</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J40" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>60</v>
@@ -3454,27 +3526,27 @@
         <v>24</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J41" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="D42" s="3" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>69</v>
@@ -3484,27 +3556,27 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>135</v>
+        <v>37</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>69</v>
@@ -3514,27 +3586,27 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J43" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="D44" s="3" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>69</v>
@@ -3544,27 +3616,27 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>199</v>
+        <v>51</v>
       </c>
       <c r="J44" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>129</v>
+        <v>198</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>69</v>
@@ -3577,51 +3649,51 @@
         <v>202</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="J46" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>129</v>
+        <v>207</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>60</v>
@@ -3634,24 +3706,24 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>208</v>
+        <v>125</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>60</v>
@@ -3664,27 +3736,27 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="J48" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>69</v>
@@ -3694,10 +3766,10 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -3705,29 +3777,29 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="J50" s="3">
         <v>2</v>
@@ -3735,16 +3807,16 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>216</v>
+        <v>125</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>219</v>
+        <v>60</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>69</v>
@@ -3754,27 +3826,27 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>221</v>
+        <v>125</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>176</v>
+        <v>131</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>69</v>
@@ -3795,43 +3867,43 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>225</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>37</v>
+        <v>227</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="J53" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>60</v>
@@ -3844,24 +3916,24 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>104</v>
+        <v>219</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>60</v>
@@ -3874,57 +3946,59 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>199</v>
+        <v>44</v>
       </c>
       <c r="J55" s="3">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>233</v>
+        <v>67</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>234</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>219</v>
+        <v>60</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>236</v>
+      </c>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J56" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>69</v>
@@ -3934,27 +4008,27 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>104</v>
+        <v>242</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>69</v>
@@ -3964,27 +4038,27 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>104</v>
+        <v>242</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>246</v>
+        <v>125</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>69</v>
@@ -3997,10 +4071,10 @@
         <v>248</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="J59" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -4014,64 +4088,64 @@
         <v>251</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>252</v>
+        <v>131</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>236</v>
+        <v>51</v>
       </c>
       <c r="J60" s="3">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>171</v>
+        <v>229</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>129</v>
+        <v>255</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>256</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>60</v>
@@ -4087,51 +4161,51 @@
         <v>257</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>150</v>
+        <v>258</v>
       </c>
       <c r="J62" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J63" s="3">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>190</v>
+        <v>235</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>60</v>
@@ -4144,13 +4218,13 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>262</v>
+        <v>51</v>
       </c>
       <c r="J64" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -4161,7 +4235,7 @@
         <v>263</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>60</v>
@@ -4177,10 +4251,10 @@
         <v>264</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4191,7 +4265,7 @@
         <v>266</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>60</v>
@@ -4207,10 +4281,10 @@
         <v>267</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>104</v>
+        <v>242</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67">
@@ -4221,13 +4295,13 @@
         <v>269</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
@@ -4237,24 +4311,24 @@
         <v>270</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="J67" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>69</v>
@@ -4264,13 +4338,13 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="I68" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="I68" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="J68" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69">
@@ -4281,10 +4355,10 @@
         <v>275</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>229</v>
+        <v>276</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>69</v>
@@ -4294,10 +4368,10 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="J69" s="3">
         <v>0</v>
@@ -4305,76 +4379,76 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>73</v>
+        <v>278</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>104</v>
+        <v>281</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>129</v>
+        <v>282</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>281</v>
+        <v>238</v>
       </c>
       <c r="J71" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>243</v>
+        <v>285</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>244</v>
+        <v>60</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>69</v>
@@ -4384,40 +4458,40 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>205</v>
+        <v>44</v>
       </c>
       <c r="J72" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>190</v>
+        <v>289</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>236</v>
+        <v>291</v>
       </c>
       <c r="J73" s="3">
         <v>23</v>
@@ -4425,46 +4499,46 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>97</v>
+        <v>292</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>289</v>
+        <v>235</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J74" s="3">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>292</v>
+        <v>244</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>293</v>
+        <v>235</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>69</v>
@@ -4474,24 +4548,24 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J75" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>296</v>
+        <v>73</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>298</v>
+        <v>205</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>60</v>
@@ -4507,10 +4581,10 @@
         <v>299</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J76" s="3">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77">
@@ -4521,10 +4595,10 @@
         <v>301</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>298</v>
+        <v>200</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>60</v>
+        <v>201</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>69</v>
@@ -4537,10 +4611,10 @@
         <v>302</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>44</v>
+        <v>242</v>
       </c>
       <c r="J77" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78">
@@ -4551,13 +4625,13 @@
         <v>304</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
@@ -4567,7 +4641,7 @@
         <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="J78" s="3">
         <v>3</v>
@@ -4575,16 +4649,16 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>306</v>
+        <v>244</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>190</v>
+        <v>245</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>60</v>
+        <v>227</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>69</v>
@@ -4597,24 +4671,24 @@
         <v>307</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>51</v>
+        <v>242</v>
       </c>
       <c r="J79" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>303</v>
+        <v>125</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>308</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>190</v>
+        <v>309</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>69</v>
@@ -4624,87 +4698,87 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>199</v>
+        <v>44</v>
       </c>
       <c r="J80" s="3">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>274</v>
+        <v>73</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>100</v>
+        <v>151</v>
       </c>
       <c r="J81" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>51</v>
+        <v>238</v>
       </c>
       <c r="J82" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>251</v>
+        <v>309</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>252</v>
+        <v>131</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>69</v>
@@ -4717,27 +4791,27 @@
         <v>316</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="J83" s="3">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>317</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
@@ -4747,24 +4821,24 @@
         <v>318</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>199</v>
+        <v>100</v>
       </c>
       <c r="J84" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>129</v>
+        <v>319</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>319</v>
+        <v>244</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>69</v>
@@ -4774,24 +4848,24 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J85" s="3">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>129</v>
+        <v>322</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>60</v>
@@ -4804,27 +4878,27 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="J86" s="3">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>325</v>
+        <v>205</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>69</v>
@@ -4837,84 +4911,84 @@
         <v>326</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="J87" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>73</v>
+        <v>327</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>298</v>
+        <v>221</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="J88" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>129</v>
+        <v>330</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>190</v>
+        <v>332</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>60</v>
+        <v>333</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>44</v>
+        <v>151</v>
       </c>
       <c r="J89" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>325</v>
+        <v>221</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>69</v>
@@ -4924,27 +4998,27 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>44</v>
+        <v>194</v>
       </c>
       <c r="J90" s="3">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>190</v>
+        <v>339</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>69</v>
@@ -4954,24 +5028,24 @@
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>199</v>
+        <v>100</v>
       </c>
       <c r="J91" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>60</v>
@@ -4984,24 +5058,24 @@
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="J92" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>60</v>
@@ -5014,27 +5088,27 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="J93" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>339</v>
+        <v>204</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>340</v>
+        <v>205</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>69</v>
@@ -5044,40 +5118,42 @@
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F95" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>349</v>
+      </c>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="J95" s="3">
         <v>0</v>
@@ -5085,119 +5161,119 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>343</v>
+        <v>125</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>345</v>
+        <v>221</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>346</v>
+        <v>69</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="J96" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>348</v>
+        <v>73</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="J97" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>351</v>
+        <v>125</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>353</v>
+        <v>235</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="J98" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>250</v>
+        <v>191</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>355</v>
+        <v>205</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="J99" s="3">
         <v>3</v>
@@ -5205,16 +5281,16 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>359</v>
+        <v>221</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>69</v>
@@ -5224,27 +5300,27 @@
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>362</v>
+        <v>225</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>244</v>
+        <v>60</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>69</v>
@@ -5254,70 +5330,70 @@
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J101" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="C102" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C102" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="D102" s="3" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>38</v>
+        <v>366</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>262</v>
+        <v>51</v>
       </c>
       <c r="J102" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="J103" s="3">
         <v>3</v>
@@ -5325,16 +5401,16 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>229</v>
+        <v>373</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>69</v>
@@ -5344,84 +5420,84 @@
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>100</v>
+        <v>219</v>
       </c>
       <c r="J104" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>171</v>
+        <v>346</v>
       </c>
       <c r="B105" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="C105" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="D105" s="3" t="s">
-        <v>244</v>
+        <v>131</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>100</v>
+        <v>238</v>
       </c>
       <c r="J105" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>375</v>
+        <v>346</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="J106" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>190</v>
+        <v>285</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>60</v>
@@ -5434,30 +5510,30 @@
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="J107" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>382</v>
+        <v>225</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
@@ -5467,7 +5543,7 @@
         <v>383</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>295</v>
+        <v>238</v>
       </c>
       <c r="J108" s="3">
         <v>22</v>
@@ -5478,26 +5554,26 @@
         <v>384</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>229</v>
+        <v>385</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>150</v>
+        <v>51</v>
       </c>
       <c r="J109" s="3">
         <v>4</v>
@@ -5505,7 +5581,7 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>387</v>
@@ -5514,7 +5590,7 @@
         <v>388</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>38</v>
@@ -5527,10 +5603,10 @@
         <v>389</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>262</v>
+        <v>100</v>
       </c>
       <c r="J110" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -5541,30 +5617,330 @@
         <v>391</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>190</v>
+        <v>392</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="J111" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J112" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J113" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J114" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="J115" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="J116" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="J117" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J118" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J119" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J120" s="3">
         <v>0</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J121" s="3">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J111"/>
+  <autoFilter ref="A1:J121"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5676,6 +6052,16 @@
     <hyperlink ref="H109" r:id="rId108"/>
     <hyperlink ref="H110" r:id="rId109"/>
     <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5683,8 +6069,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5717,13 +6103,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5731,56 +6117,56 @@
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>103</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>130</v>
+        <v>212</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>145</v>
+        <v>226</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>146</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>188</v>
+        <v>274</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>189</v>
+        <v>275</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5788,18 +6174,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>191</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>206</v>
+        <v>311</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5807,18 +6193,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>207</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>129</v>
+        <v>330</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>211</v>
+        <v>331</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>194</v>
+        <v>332</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5826,18 +6212,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>212</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>216</v>
+        <v>344</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5845,18 +6231,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>220</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>227</v>
+        <v>348</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5864,18 +6250,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>230</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>237</v>
+        <v>73</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>238</v>
+        <v>353</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>239</v>
+        <v>189</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5883,18 +6269,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>240</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>241</v>
+        <v>416</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>242</v>
+        <v>417</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>243</v>
+        <v>205</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5902,258 +6288,11 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G24"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6165,19 +6304,6 @@
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
-    <hyperlink ref="G22" r:id="rId21"/>
-    <hyperlink ref="G23" r:id="rId22"/>
-    <hyperlink ref="G24" r:id="rId23"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6191,23 +6317,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>395</v>
+        <v>236</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="B3" s="3">
         <v>27</v>
@@ -6215,39 +6341,39 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="B4" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>400</v>
+        <v>349</v>
       </c>
       <c r="B8" s="3">
         <v>19</v>
@@ -6255,15 +6381,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="B10" s="3">
         <v>17</v>
@@ -6271,7 +6397,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="B11" s="3">
         <v>16</v>
@@ -6279,15 +6405,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="B12" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
@@ -6295,7 +6421,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="B14" s="3">
         <v>9</v>
@@ -6303,7 +6429,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6311,10 +6437,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6324,7 +6450,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6333,7 +6459,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2">
@@ -6346,7 +6472,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="B3" s="3">
         <v>6</v>
@@ -6354,55 +6480,55 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>68</v>
+        <v>244</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>101</v>
+        <v>160</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>175</v>
+        <v>58</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6410,7 +6536,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>196</v>
+        <v>114</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6418,7 +6544,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>214</v>
+        <v>147</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6426,7 +6552,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6434,7 +6560,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>250</v>
+        <v>188</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6442,7 +6568,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6450,7 +6576,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6471,16 +6597,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2">
@@ -6488,10 +6614,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3">
-        <v>22.7</v>
+        <v>19.4</v>
       </c>
       <c r="D2" s="3">
         <v>6</v>
@@ -6502,10 +6628,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="C3" s="3">
-        <v>19.4</v>
+        <v>17.3</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
@@ -6516,13 +6642,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="C4" s="3">
-        <v>17.3</v>
+        <v>14.7</v>
       </c>
       <c r="D4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -6530,7 +6656,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C5" s="3">
         <v>14.0</v>
@@ -6544,7 +6670,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C6" s="3">
         <v>11.2</v>
@@ -6572,10 +6698,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="C8" s="3">
-        <v>7.0</v>
+        <v>7.3</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -6586,10 +6712,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="C9" s="3">
-        <v>6.2</v>
+        <v>7.0</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -6600,13 +6726,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="C10" s="3">
-        <v>2.8</v>
+        <v>7.0</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -6614,13 +6740,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="C11" s="3">
-        <v>2.8</v>
+        <v>7.0</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -6628,10 +6754,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>250</v>
+        <v>114</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="D12" s="3">
         <v>2</v>
@@ -6642,13 +6768,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="C13" s="3">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6656,13 +6782,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="C14" s="3">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6670,10 +6796,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6684,13 +6810,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>225</v>
+        <v>156</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6710,15 +6836,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>413</v>
+        <v>439</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -6732,10 +6858,10 @@
         <v>69</v>
       </c>
       <c r="B3" s="3">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>414</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4">
@@ -6743,10 +6869,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -6765,7 +6891,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2">
@@ -6773,15 +6899,15 @@
         <v>60</v>
       </c>
       <c r="B2" s="3">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -6789,12 +6915,12 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>244</v>
+        <v>175</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6802,7 +6928,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>176</v>
+        <v>227</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6810,15 +6936,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>219</v>
+        <v>333</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>252</v>
+        <v>201</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -6826,7 +6952,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6841,8 +6967,8 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -6853,10 +6979,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6868,10 +6994,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6888,7 +7014,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>79</v>
@@ -6897,19 +7023,19 @@
         <v>80</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6920,31 +7046,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="F3" s="3">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>428</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4">
@@ -6952,31 +7078,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>430</v>
+        <v>372</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>190</v>
+        <v>455</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
       <c r="F4" s="3">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -6984,31 +7110,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>434</v>
+        <v>459</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="F5" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>438</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -7016,31 +7142,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F6" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>72</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7">
@@ -7048,31 +7174,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>161</v>
+        <v>469</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>162</v>
+        <v>245</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>420</v>
+        <v>470</v>
       </c>
       <c r="F7" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8">
@@ -7080,28 +7206,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>447</v>
+        <v>473</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>448</v>
+        <v>160</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>449</v>
+        <v>161</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="F8" s="3">
         <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>44</v>
@@ -7112,31 +7238,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="F9" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>455</v>
+        <v>479</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>44</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10">
@@ -7144,31 +7270,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>456</v>
+        <v>480</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>457</v>
+        <v>481</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>243</v>
+        <v>482</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F10" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>459</v>
+        <v>484</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>295</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -7176,31 +7302,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>434</v>
+        <v>485</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>229</v>
+        <v>487</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="F11" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -7208,28 +7334,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>464</v>
+        <v>491</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F12" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>465</v>
+        <v>492</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>44</v>
@@ -7240,31 +7366,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="F13" s="3">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>100</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14">
@@ -7272,31 +7398,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F14" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>236</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -7304,31 +7430,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>444</v>
+        <v>501</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>79</v>
+        <v>502</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="F15" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>475</v>
+        <v>503</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>476</v>
+        <v>504</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>199</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -7336,31 +7462,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>477</v>
+        <v>449</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>118</v>
+        <v>395</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>478</v>
+        <v>388</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="F16" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>479</v>
+        <v>505</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>199</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -7368,31 +7494,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>482</v>
+        <v>79</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>483</v>
+        <v>80</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="F17" s="3">
         <v>30</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>485</v>
+        <v>508</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>438</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18">
@@ -7400,31 +7526,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>486</v>
+        <v>509</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>352</v>
+        <v>114</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="F18" s="3">
+        <v>30</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="F18" s="3">
-        <v>28</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="19">
@@ -7432,31 +7558,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>447</v>
+        <v>513</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>489</v>
+        <v>514</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>218</v>
+        <v>320</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>491</v>
+        <v>516</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>492</v>
+        <v>467</v>
       </c>
     </row>
     <row r="20">
@@ -7464,31 +7590,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>193</v>
+        <v>387</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="F20" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>494</v>
+        <v>518</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>495</v>
+        <v>519</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>44</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21">
@@ -7496,31 +7622,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>471</v>
+        <v>520</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>496</v>
+        <v>521</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>353</v>
+        <v>221</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>497</v>
+        <v>522</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>199</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W24.xlsx
+++ b/reports/devops-jobs-israel-2026-W24.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="512">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-12T10:37:26</t>
+    <t xml:space="preserve">2026-06-14T09:52:04</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8%</t>
+    <t xml:space="preserve">0.9%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -159,24 +159,21 @@
     <t xml:space="preserve">Cloud Architect</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4855504101?gh_jid=4855504101</t>
+    <t xml:space="preserve">Azure, Networking, Security, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4888525101?gh_jid=4888525101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
   </si>
   <si>
     <t xml:space="preserve">Senior Cloud Architect</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure, Networking, Security, AI/MLOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4883675101?gh_jid=4883675101</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
     <t xml:space="preserve">Solution Architect</t>
   </si>
   <si>
@@ -210,7 +207,7 @@
     <t xml:space="preserve">https://unity.com/careers/positions/7911982?gh_jid=7911982</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Developer Operations Engineer</t>
+    <t xml:space="preserve">Senior DevOps Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Python, Prometheus, Grafana, ELK/Elastic, Pulumi, CloudFormation, Kafka, Networking, Security, Argo CD, Observability, Airflow, Spark</t>
@@ -240,9 +237,6 @@
     <t xml:space="preserve">2026-06-03</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
   </si>
   <si>
@@ -312,9 +306,21 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gongio</t>
   </si>
   <si>
+    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
   </si>
   <si>
@@ -336,6 +342,15 @@
     <t xml:space="preserve">2026-05-28</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
     <t xml:space="preserve">Software Architect - DevOps Group</t>
   </si>
   <si>
@@ -465,229 +480,568 @@
     <t xml:space="preserve">Riskified</t>
   </si>
   <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587301002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Platform Engineer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lisbon</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4426065244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest acq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-acq-4427190837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vi-4421931598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4422246034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfraEdge IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infraedge-il-4421944139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VoIP/DevOps Engineer (SIP Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Squaretalk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/voip-devops-engineer-sip-focus-at-squaretalk-4426348262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-abra-4425998329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4428600414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CorrActions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-devops-engineer-at-corractions-4423612672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4395485460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentee Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-mentee-robotics-4422793922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4421593110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aman Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aman-group-4423678087</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraud Group Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-abra-4425003795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4422246034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
+    <t xml:space="preserve">DevOps Engineer (25078)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25078-at-yael-group-4423652623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4427156928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bynet-data-communications-4423131095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ur-tech-jobs-4425565373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4425736215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mastercard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-mastercard-4421916027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagomi Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-nagomi-security-4425014911</t>
   </si>
   <si>
     <t xml:space="preserve">CodeValue</t>
   </si>
   <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4425198243</t>
   </si>
   <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest acq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-acq-4427190837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
+    <t xml:space="preserve">Senior Azure DevOps &amp; Release Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-azure-devops-release-engineer-at-abra-4426234726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-millennium-4425034300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Nexite</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4425654229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Administrator &amp; DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appdome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-administrator-devops-at-appdome-4421928922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4426065244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aman Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aman-group-4423678087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VoIP/DevOps Engineer (SIP Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Squaretalk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/voip-devops-engineer-sip-focus-at-squaretalk-4426348262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4427054576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-quanthealth-4425994726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sola Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sola-security-4425029092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-quantum-machines-4412371822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-logica-it-4423649420</t>
   </si>
   <si>
     <t xml:space="preserve">Nogamy</t>
@@ -696,696 +1050,261 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4427161800</t>
   </si>
   <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ata, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4395474406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-quanthealth-4425994726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-quantum-machines-4412371822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4421926577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Infrastructure Engineer（SRE）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">株式会社GA technologies / GA technologies Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-infrastructure-engineer%EF%BC%88sre%EF%BC%89-at-%E6%A0%AA%E5%BC%8F%E4%BC%9A%E7%A4%BEga-technologies-ga-technologies-co-ltd-4425654538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tekgence Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4426102112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-infrastructure-engineer-at-comblack-4425497939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-extreme-4426777242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Squad Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-squad-leader-at-milestone-systems-4427508430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Hai, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-platform-engineer-at-gotfriends-4421571443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stampli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-stampli-4427522493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kroll Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-kroll-consulting-4428396808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
   </si>
   <si>
     <t xml:space="preserve">Security</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-coralogix-4368406182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfraEdge IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infraedge-il-4421944139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paz - yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yaqum, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-paz-yellow-4425456877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4427156928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vi-4421931598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sola Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sola-security-4425029092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bynet-data-communications-4423131095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4415530326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Automation &amp; Release Engineering Specialist (25103)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-automation-release-engineering-specialist-25103-at-yael-group-4424811001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeva Systems</t>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
   </si>
   <si>
     <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mastercard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-mastercard-4421916027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Infrastructure Engineer（SRE）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">株式会社GA technologies / GA technologies Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-infrastructure-engineer%EF%BC%88sre%EF%BC%89-at-%E6%A0%AA%E5%BC%8F%E4%BC%9A%E7%A4%BEga-technologies-ga-technologies-co-ltd-4425654538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4427516055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentee Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-mentee-robotics-4422793922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagomi Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-nagomi-security-4425014911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lenovo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-lenovo-4424600261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CorrActions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-devops-engineer-at-corractions-4423612672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer (Compute Runtime)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CyberArk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-compute-runtime-at-cyberark-4405971728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural Intelligence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (25078)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25078-at-yael-group-4423652623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4427054576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Azure DevOps &amp; Release Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-azure-devops-release-engineer-at-abra-4426234726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4421593110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-logica-it-4423649420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4421926577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-ai-4422235857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tekgence Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4426102112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4425543714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4425076264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4425237881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer - 236606</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT / Cloud Specialist - 235226</t>
   </si>
   <si>
     <t xml:space="preserve">Experis Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-236606-at-experis-israel-4422794863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4417041575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-elbit-systems-israel-4421911706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-extreme-4426777242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/phy-system-engineer-at-parallel-wireless-4407105512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-infrastructure-engineer-at-comblack-4425497939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Squad Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-squad-leader-at-milestone-systems-4427508430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-commit-4425110784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Hai, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ur-tech-jobs-4425565373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (U.S Citizen)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLIGO Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-u-s-citizen-at-oligo-security-4427007687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stampli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-stampli-4427522493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-platform-engineer-at-gotfriends-4421571443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT / Cloud Specialist - 235226</t>
-  </si>
-  <si>
     <t xml:space="preserve">Haifa, Haifa District, Israel</t>
   </si>
   <si>
@@ -1410,111 +1329,117 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
   </si>
   <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-candex-4410031859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Fortinet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fortinet-4393535304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure &amp; Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Squadron Israel - Hatayeset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-technical-support-specialist-at-the-squadron-israel-hatayeset-4421938671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bria AI</t>
   </si>
   <si>
@@ -1524,6 +1449,30 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-codevalue-4421843930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI Operations Engineer</t>
   </si>
   <si>
@@ -1536,10 +1485,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-comblack-4425486490</t>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
   </si>
   <si>
     <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
@@ -1548,51 +1500,6 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
   </si>
   <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1617,7 +1524,10 @@
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
+    <t xml:space="preserve">Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1769,7 +1679,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7">
@@ -1777,7 +1687,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1785,7 +1695,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -1793,7 +1703,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>575</v>
+        <v>583</v>
       </c>
     </row>
     <row r="10">
@@ -1865,7 +1775,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -1873,7 +1783,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1892,36 +1802,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>438</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="B2" s="3">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>451</v>
+        <v>419</v>
       </c>
       <c r="B3" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1929,7 +1839,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>524</v>
+        <v>493</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1948,130 +1858,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>421</v>
+        <v>390</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>525</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>526</v>
+        <v>495</v>
       </c>
       <c r="B2" s="3">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>527</v>
+        <v>496</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>433</v>
+        <v>497</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>528</v>
+        <v>398</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>529</v>
+        <v>498</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>432</v>
+        <v>499</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>530</v>
+        <v>402</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>531</v>
+        <v>314</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>423</v>
+        <v>500</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>349</v>
+        <v>501</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>532</v>
+        <v>396</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>429</v>
+        <v>502</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2096,13 +2006,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>533</v>
+        <v>503</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>534</v>
+        <v>504</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>535</v>
+        <v>505</v>
       </c>
     </row>
     <row r="2">
@@ -2110,13 +2020,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3">
-        <v>17.5</v>
+        <v>13.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>536</v>
+        <v>506</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2125,88 +2035,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3">
-        <v>38.3</v>
+        <v>34.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>536</v>
+        <v>506</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>537</v>
+        <v>507</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.3</v>
+        <v>7.6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>536</v>
+        <v>506</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>538</v>
+        <v>508</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>536</v>
+        <v>506</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>30.0</v>
+        <v>33.3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>536</v>
+        <v>506</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.4</v>
+        <v>16.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>536</v>
+        <v>506</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>541</v>
+        <v>511</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>13.9</v>
+        <v>15.5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>536</v>
+        <v>506</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2217,7 +2127,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
     <col min="2" max="2" width="49" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -2290,7 +2200,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -2322,7 +2232,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -2351,15 +2261,15 @@
         <v>47</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J4" s="3">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>35</v>
@@ -2374,7 +2284,7 @@
         <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>24</v>
@@ -2383,15 +2293,15 @@
         <v>50</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J5" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>35</v>
@@ -2406,24 +2316,24 @@
         <v>38</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J6" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>35</v>
@@ -2438,644 +2348,644 @@
         <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="J9" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="J10" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J16" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="J18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J19" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="J20" s="3">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="J21" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="J22" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>114</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="J23" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="J24" s="3">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="J25" s="3">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>132</v>
@@ -3084,602 +2994,604 @@
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="J28" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J29" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
       <c r="J30" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>151</v>
+        <v>102</v>
       </c>
       <c r="J31" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="J32" s="3">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>155</v>
+        <v>66</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="J33" s="3">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>146</v>
+        <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>160</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J35" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="J36" s="3">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J37" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>175</v>
+        <v>59</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="G38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J38" s="3">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>179</v>
+        <v>44</v>
       </c>
       <c r="J39" s="3">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>60</v>
+        <v>176</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>60</v>
+        <v>176</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>182</v>
-      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="J40" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F41" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>183</v>
+      </c>
       <c r="G41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="J41" s="3">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>189</v>
+        <v>59</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>146</v>
+        <v>44</v>
       </c>
       <c r="J42" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>51</v>
+        <v>195</v>
       </c>
       <c r="J44" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>201</v>
+        <v>59</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J45" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>60</v>
+        <v>202</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="J46" s="3">
         <v>3</v>
@@ -3687,67 +3599,67 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>207</v>
+        <v>130</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J47" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>125</v>
+        <v>206</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>212</v>
@@ -3756,10 +3668,10 @@
         <v>213</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
@@ -3769,87 +3681,87 @@
         <v>214</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="D50" s="3" t="s">
-        <v>175</v>
+        <v>37</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="J50" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="J51" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>125</v>
+        <v>221</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="D52" s="3" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
@@ -3859,27 +3771,27 @@
         <v>224</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
@@ -3889,10 +3801,10 @@
         <v>228</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54">
@@ -3903,192 +3815,190 @@
         <v>230</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>219</v>
+        <v>99</v>
       </c>
       <c r="J54" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>125</v>
+        <v>233</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>44</v>
+        <v>236</v>
       </c>
       <c r="J55" s="3">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>67</v>
+        <v>237</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>236</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>238</v>
+        <v>99</v>
       </c>
       <c r="J56" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>242</v>
+        <v>102</v>
       </c>
       <c r="J57" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>227</v>
+        <v>136</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>242</v>
+        <v>102</v>
       </c>
       <c r="J58" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="J59" s="3">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>249</v>
+        <v>62</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>131</v>
+        <v>37</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>38</v>
@@ -4101,87 +4011,87 @@
         <v>252</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="J60" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>221</v>
+        <v>254</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>60</v>
+        <v>255</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>255</v>
+        <v>171</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>258</v>
+        <v>102</v>
       </c>
       <c r="J62" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
@@ -4191,24 +4101,24 @@
         <v>260</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>51</v>
+        <v>151</v>
       </c>
       <c r="J63" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>261</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>38</v>
@@ -4221,84 +4131,84 @@
         <v>262</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J64" s="3">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>263</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>221</v>
+        <v>264</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>60</v>
+        <v>176</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>100</v>
+        <v>266</v>
       </c>
       <c r="J65" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="J66" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>268</v>
+        <v>56</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>38</v>
@@ -4308,60 +4218,60 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>100</v>
+        <v>272</v>
       </c>
       <c r="J67" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>125</v>
+        <v>273</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>273</v>
+        <v>102</v>
       </c>
       <c r="J68" s="3">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>274</v>
+        <v>62</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>276</v>
+        <v>189</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
@@ -4371,54 +4281,54 @@
         <v>277</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>151</v>
+        <v>102</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>279</v>
-      </c>
       <c r="C70" s="3" t="s">
-        <v>205</v>
+        <v>239</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>281</v>
+        <v>225</v>
       </c>
       <c r="J70" s="3">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>225</v>
+        <v>281</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>38</v>
@@ -4428,147 +4338,147 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>238</v>
+        <v>102</v>
       </c>
       <c r="J71" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>285</v>
+        <v>219</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="J72" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>289</v>
+        <v>197</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="J73" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>51</v>
+        <v>236</v>
       </c>
       <c r="J74" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>297</v>
+        <v>210</v>
       </c>
       <c r="J75" s="3">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>73</v>
+        <v>292</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>298</v>
+        <v>251</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>38</v>
@@ -4578,253 +4488,255 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>44</v>
+        <v>272</v>
       </c>
       <c r="J76" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>201</v>
+        <v>59</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="J77" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>205</v>
+        <v>299</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>194</v>
+        <v>301</v>
       </c>
       <c r="J78" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>245</v>
+        <v>193</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>227</v>
+        <v>59</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>242</v>
+        <v>48</v>
       </c>
       <c r="J79" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>125</v>
+        <v>305</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>308</v>
+        <v>212</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>309</v>
+        <v>193</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
       <c r="J80" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>73</v>
+        <v>308</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>238</v>
+        <v>48</v>
       </c>
       <c r="J82" s="3">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H83" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>316</v>
-      </c>
       <c r="I83" s="3" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="J83" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>170</v>
+        <v>233</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="I84" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="I84" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85">
@@ -4832,16 +4744,16 @@
         <v>319</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>244</v>
+        <v>320</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>320</v>
+        <v>239</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>131</v>
+        <v>240</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
@@ -4851,356 +4763,354 @@
         <v>321</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>51</v>
+        <v>272</v>
       </c>
       <c r="J85" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>323</v>
-      </c>
       <c r="C86" s="3" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J86" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>194</v>
+        <v>122</v>
       </c>
       <c r="J87" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>328</v>
-      </c>
       <c r="C88" s="3" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>330</v>
+        <v>130</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>331</v>
+        <v>207</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>332</v>
+        <v>208</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>333</v>
+        <v>136</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>125</v>
+        <v>273</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="J90" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>339</v>
+        <v>231</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="J91" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>341</v>
+        <v>62</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J92" s="3">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>344</v>
+        <v>130</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>275</v>
+        <v>337</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="J93" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>346</v>
+        <v>62</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>204</v>
+        <v>339</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>100</v>
+        <v>266</v>
       </c>
       <c r="J94" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>348</v>
+        <v>130</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>188</v>
+        <v>341</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>349</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>151</v>
+        <v>102</v>
       </c>
       <c r="J95" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="J96" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>73</v>
+        <v>345</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>38</v>
@@ -5210,130 +5120,130 @@
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>151</v>
+        <v>191</v>
       </c>
       <c r="J97" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>51</v>
+        <v>272</v>
       </c>
       <c r="J98" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="J99" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>360</v>
+        <v>212</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>221</v>
+        <v>254</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>60</v>
+        <v>255</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="J100" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>225</v>
+        <v>355</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="J101" s="3">
         <v>3</v>
@@ -5341,149 +5251,149 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>365</v>
+        <v>197</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>366</v>
+        <v>68</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>51</v>
+        <v>191</v>
       </c>
       <c r="J102" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="J103" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>372</v>
+        <v>212</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>69</v>
+        <v>364</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="J104" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>375</v>
+        <v>251</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>373</v>
+        <v>197</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="J105" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>205</v>
+        <v>370</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="J106" s="3">
         <v>3</v>
@@ -5491,46 +5401,46 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>285</v>
+        <v>374</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="J107" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>205</v>
+        <v>377</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>38</v>
@@ -5540,407 +5450,137 @@
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="J108" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>244</v>
+        <v>380</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>385</v>
+        <v>197</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>51</v>
+        <v>301</v>
       </c>
       <c r="J109" s="3">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>387</v>
+        <v>259</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>388</v>
+        <v>189</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>100</v>
+        <v>151</v>
       </c>
       <c r="J110" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>392</v>
+        <v>197</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>117</v>
+        <v>266</v>
       </c>
       <c r="J111" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>219</v>
+        <v>99</v>
       </c>
       <c r="J112" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="I113" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J113" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="I114" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="J114" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="I115" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="J115" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="J116" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="I117" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="J117" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="I118" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="J118" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J119" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F120" s="3"/>
-      <c r="G120" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="I120" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J120" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F121" s="3"/>
-      <c r="G121" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="I121" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="J121" s="3">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J121"/>
+  <autoFilter ref="A1:J112"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -6053,15 +5693,6 @@
     <hyperlink ref="H110" r:id="rId109"/>
     <hyperlink ref="H111" r:id="rId110"/>
     <hyperlink ref="H112" r:id="rId111"/>
-    <hyperlink ref="H113" r:id="rId112"/>
-    <hyperlink ref="H114" r:id="rId113"/>
-    <hyperlink ref="H115" r:id="rId114"/>
-    <hyperlink ref="H116" r:id="rId115"/>
-    <hyperlink ref="H117" r:id="rId116"/>
-    <hyperlink ref="H118" r:id="rId117"/>
-    <hyperlink ref="H119" r:id="rId118"/>
-    <hyperlink ref="H120" r:id="rId119"/>
-    <hyperlink ref="H121" r:id="rId120"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6069,9 +5700,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -6103,13 +5734,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -6117,56 +5748,56 @@
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>213</v>
+        <v>59</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>214</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>226</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>228</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>274</v>
+        <v>229</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>275</v>
+        <v>230</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>276</v>
+        <v>231</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -6174,18 +5805,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>277</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>73</v>
+        <v>237</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>311</v>
+        <v>238</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>205</v>
+        <v>239</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -6193,18 +5824,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>312</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>330</v>
+        <v>62</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>331</v>
+        <v>251</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>332</v>
+        <v>216</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6212,18 +5843,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>334</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>344</v>
+        <v>283</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6231,18 +5862,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>345</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>348</v>
+        <v>387</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>188</v>
+        <v>388</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6250,49 +5881,11 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>418</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6302,8 +5895,6 @@
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6317,23 +5908,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>421</v>
+        <v>390</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>422</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>236</v>
+        <v>392</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
       <c r="B3" s="3">
         <v>27</v>
@@ -6341,7 +5932,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="B4" s="3">
         <v>26</v>
@@ -6349,7 +5940,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>425</v>
+        <v>395</v>
       </c>
       <c r="B5" s="3">
         <v>23</v>
@@ -6357,15 +5948,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B7" s="3">
         <v>19</v>
@@ -6373,7 +5964,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>349</v>
+        <v>314</v>
       </c>
       <c r="B8" s="3">
         <v>19</v>
@@ -6381,15 +5972,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="B9" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="B10" s="3">
         <v>17</v>
@@ -6397,7 +5988,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="B11" s="3">
         <v>16</v>
@@ -6405,15 +5996,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="B12" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
@@ -6421,7 +6012,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="B14" s="3">
         <v>9</v>
@@ -6429,7 +6020,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>433</v>
+        <v>403</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6437,10 +6028,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>434</v>
+        <v>404</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6450,7 +6041,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6459,7 +6050,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>435</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2">
@@ -6472,7 +6063,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B3" s="3">
         <v>6</v>
@@ -6480,7 +6071,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -6488,7 +6079,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>225</v>
+        <v>96</v>
       </c>
       <c r="B5" s="3">
         <v>5</v>
@@ -6496,7 +6087,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
@@ -6504,15 +6095,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>160</v>
+        <v>251</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -6520,7 +6111,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -6528,7 +6119,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6536,7 +6127,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6544,7 +6135,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6552,7 +6143,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6560,7 +6151,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6568,7 +6159,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>191</v>
+        <v>230</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6576,7 +6167,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6597,16 +6188,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>436</v>
+        <v>406</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>435</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2">
@@ -6614,13 +6205,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="C2" s="3">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="D2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -6628,7 +6219,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3">
         <v>17.3</v>
@@ -6642,13 +6233,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="C4" s="3">
-        <v>14.7</v>
+        <v>17.3</v>
       </c>
       <c r="D4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -6656,13 +6247,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="C5" s="3">
-        <v>14.0</v>
+        <v>14.7</v>
       </c>
       <c r="D5" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -6670,10 +6261,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -6684,10 +6275,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="C7" s="3">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="D7" s="3">
         <v>3</v>
@@ -6698,7 +6289,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C8" s="3">
         <v>7.3</v>
@@ -6712,7 +6303,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="3">
         <v>7.0</v>
@@ -6726,7 +6317,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="C10" s="3">
         <v>7.0</v>
@@ -6740,13 +6331,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>244</v>
+        <v>119</v>
       </c>
       <c r="C11" s="3">
-        <v>7.0</v>
+        <v>6.2</v>
       </c>
       <c r="D11" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6754,13 +6345,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>114</v>
+        <v>251</v>
       </c>
       <c r="C12" s="3">
-        <v>6.2</v>
+        <v>6.0</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -6768,7 +6359,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
       <c r="C13" s="3">
         <v>3.1</v>
@@ -6782,7 +6373,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -6796,7 +6387,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="C15" s="3">
         <v>2.8</v>
@@ -6810,7 +6401,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C16" s="3">
         <v>2.6</v>
@@ -6836,15 +6427,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>438</v>
+        <v>408</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>439</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -6855,13 +6446,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>440</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4">
@@ -6872,7 +6463,7 @@
         <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>441</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -6891,23 +6482,23 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>438</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="3">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -6915,12 +6506,12 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6928,7 +6519,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6936,15 +6527,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>333</v>
+        <v>202</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>201</v>
+        <v>255</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -6952,7 +6543,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6967,8 +6558,8 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="43" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -6979,10 +6570,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>436</v>
+        <v>406</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6994,10 +6585,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>444</v>
+        <v>414</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -7014,28 +6605,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>445</v>
+        <v>415</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>447</v>
+        <v>417</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>448</v>
+        <v>418</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -7046,31 +6637,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>449</v>
+        <v>326</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>450</v>
+        <v>357</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>451</v>
+        <v>419</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>452</v>
+        <v>420</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>453</v>
+        <v>358</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4">
@@ -7078,31 +6669,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>454</v>
+        <v>421</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>372</v>
+        <v>422</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>455</v>
+        <v>423</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="F4" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>457</v>
+        <v>424</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>458</v>
+        <v>425</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>100</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5">
@@ -7110,31 +6701,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>459</v>
+        <v>426</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>460</v>
+        <v>427</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>205</v>
+        <v>428</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="F5" s="3">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>461</v>
+        <v>430</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>462</v>
+        <v>431</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
@@ -7142,31 +6733,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>463</v>
+        <v>432</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>464</v>
+        <v>433</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="F6" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>466</v>
+        <v>435</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>467</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -7174,31 +6765,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>468</v>
+        <v>436</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>469</v>
+        <v>437</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="F7" s="3">
         <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>471</v>
+        <v>439</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>472</v>
+        <v>440</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>281</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8">
@@ -7206,31 +6797,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>160</v>
+        <v>442</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>161</v>
+        <v>231</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="F8" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>474</v>
+        <v>443</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -7238,31 +6829,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>476</v>
+        <v>445</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>477</v>
+        <v>446</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="F9" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>478</v>
+        <v>447</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>479</v>
+        <v>448</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>467</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -7270,28 +6861,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>480</v>
+        <v>449</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>481</v>
+        <v>164</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>482</v>
+        <v>165</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="F10" s="3">
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -7302,31 +6893,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>485</v>
+        <v>449</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>486</v>
+        <v>452</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>487</v>
+        <v>197</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="F11" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>488</v>
+        <v>450</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>100</v>
+        <v>454</v>
       </c>
     </row>
     <row r="12">
@@ -7334,31 +6925,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>490</v>
+        <v>455</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>491</v>
+        <v>456</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="F12" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>492</v>
+        <v>457</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>493</v>
+        <v>458</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>44</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13">
@@ -7366,31 +6957,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>494</v>
+        <v>459</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>495</v>
+        <v>460</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>332</v>
+        <v>461</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>451</v>
+        <v>416</v>
       </c>
       <c r="F13" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>291</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -7398,31 +6989,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="F14" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
@@ -7430,31 +7021,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>451</v>
+        <v>419</v>
       </c>
       <c r="F15" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>100</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16">
@@ -7462,31 +7053,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>395</v>
+        <v>473</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>388</v>
+        <v>189</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>451</v>
+        <v>416</v>
       </c>
       <c r="F16" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>505</v>
+        <v>474</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17">
@@ -7494,31 +7085,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>80</v>
+        <v>477</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="F17" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>507</v>
+        <v>478</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>508</v>
+        <v>479</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18">
@@ -7526,31 +7117,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>509</v>
+        <v>480</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>114</v>
+        <v>481</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>510</v>
+        <v>197</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="F18" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>512</v>
+        <v>483</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>194</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -7558,31 +7149,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>513</v>
+        <v>484</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>514</v>
+        <v>485</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>320</v>
+        <v>193</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="F19" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>515</v>
+        <v>486</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>516</v>
+        <v>487</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>467</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20">
@@ -7590,31 +7181,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>517</v>
+        <v>476</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>387</v>
+        <v>488</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>189</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>451</v>
+        <v>419</v>
       </c>
       <c r="F20" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>518</v>
+        <v>489</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>519</v>
+        <v>490</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>291</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21">
@@ -7622,31 +7213,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>520</v>
+        <v>449</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>521</v>
+        <v>77</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="F21" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>522</v>
+        <v>491</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>523</v>
+        <v>492</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>72</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
